--- a/SAP_Field_Mapping.xlsx
+++ b/SAP_Field_Mapping.xlsx
@@ -3692,32 +3692,32 @@
       <c r="F15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>SupplierInvoiceCollection</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>LifeCycleStatusCode</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>(filter only, not mapped)</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>account.move</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Excludes Paid=12/Canceled=9/Voided=7 for account_move_open_vendor.csv</t>
         </is>
@@ -11120,32 +11120,32 @@
       <c r="F107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="4" t="inlineStr">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>RPBUPATAXNUMBERS_Q0001QueryResults</t>
         </is>
       </c>
-      <c r="B108" s="4" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>CBUPA_UUID</t>
         </is>
       </c>
-      <c r="C108" s="4" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>1001704</t>
         </is>
       </c>
-      <c r="D108" s="4" t="inlineStr">
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>(join key to CBP_UUID)</t>
         </is>
       </c>
-      <c r="E108" s="4" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="F108" s="4" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>RPBUPATAXNUMBERS side</t>
         </is>
@@ -12888,32 +12888,32 @@
       <c r="F17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>OpportunityCollection</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>LifeCycleStatusCode</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>(filter only, not mapped)</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>crm.lead</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>1/2=Open, 4/5=Won/Lost - used to split crm_lead_open.csv / crm_lead_closed.csv</t>
         </is>
@@ -13968,32 +13968,32 @@
       <c r="F17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>OpportunityCollection</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>LifeCycleStatusCode</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>(filter only, not mapped)</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>crm.lead</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>1/2=Open, 4/5=Won/Lost - used to split crm_lead_open.csv / crm_lead_closed.csv</t>
         </is>
@@ -15048,32 +15048,32 @@
       <c r="F17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>OpportunityCollection</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>LifeCycleStatusCode</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>(filter only, not mapped)</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>crm.lead</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>1/2=Open, 4/5=Won/Lost - used to split crm_lead_open.csv / crm_lead_closed.csv</t>
         </is>
@@ -16128,32 +16128,32 @@
       <c r="F11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>LocationCollection</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>InventoryManagedLocationIndicator</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>(filter only, not mapped)</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>stock.warehouse</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>True = this location becomes a warehouse row</t>
         </is>
@@ -23056,32 +23056,32 @@
       <c r="F87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>RPBUPATAXNUMBERS_Q0001QueryResults</t>
         </is>
       </c>
-      <c r="B88" s="4" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>CBUPA_UUID</t>
         </is>
       </c>
-      <c r="C88" s="4" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>1001704</t>
         </is>
       </c>
-      <c r="D88" s="4" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>(join key to CBP_UUID)</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="F88" s="4" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>RPBUPATAXNUMBERS side</t>
         </is>
@@ -26650,32 +26650,32 @@
       <c r="F15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>SupplierInvoiceCollection</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>LifeCycleStatusCode</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>(filter only, not mapped)</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>account.move</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Excludes Paid=12/Canceled=9/Voided=7 for account_move_open_vendor.csv</t>
         </is>
@@ -28402,11 +28402,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="41" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -28430,7 +28430,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>REAL DATA, FULL FIELD COVERAGE: all real per-material entities in vmumaterial checked (78 entity sets total) - MaterialCollection (base), TextCollection (detailed description, 2172/3058), PurchasingCollection/SalesCollection (UOM + purchase_ok/sale_ok), ProductCategoryCollection (category, 3058/3058 resolved), vmumaterialvaluationdata (cost price, 994/3058). No barcode/weight/dimension data exists on this tenant (GlobalTradeItemNumberCollection and QuantityCharacteristicCollection both confirmed 0 rows live) - not fabricated, left blank.</t>
+          <t>REAL DATA, FULL FIELD COVERAGE: all 15 real (non-empty) per-material entities in vmumaterial/vmumaterialvaluationdata checked (78 entity sets total exist; 172 distinct SAP fields across the 15 real ones) - MaterialCollection (base), TextCollection (detailed description, 2172/3058), PurchasingCollection/SalesCollection (UOM + purchase_ok/sale_ok), ProductCategoryCollection (category, 3058/3058 resolved), PlanningCollection (ProcurementTypeCode -&gt; route_ids/id, real 107/93 Buy/Manufacture split), IdentificationCollection/LogisticsCollection/ValuationCollection/AvailabilityConfirmationCollection/PlanningForecastGroupCollection/QuantityConversionCollection/DeviantTaxClassificationCollection (extracted, no corresponding core Odoo product.template field - see SAP_Field_Mapping.xlsx sheet 57 for exactly which), vmumaterialvaluationdata (cost price, 994/3058). No barcode/weight/dimension data exists on this tenant (GlobalTradeItemNumberCollection and QuantityCharacteristicCollection both confirmed 0 rows live) - not fabricated, left blank.</t>
         </is>
       </c>
     </row>
@@ -28636,32 +28636,36 @@
       <c r="F11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>MaterialCollection</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>IdentifiedStockTypeCode</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>tracking</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>product.template</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>'01' (Batch) -&gt; 'lot', else 'none' - real distinct value on only 1/3058 materials on this tenant</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -28892,32 +28896,32 @@
       <c r="F20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>MaterialCollection</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>00163E74-9C6C-1ED8-BF9F-5D3D00C1D488</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>(join key)</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>product.template</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Links to vmumaterialvaluationdata's MaterialUUID</t>
         </is>
@@ -29256,32 +29260,32 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>TextCollection</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>TypeCode</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>10006</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>(filter only, not mapped)</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>product.template</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>TextCollection - only TypeCode=10006 rows are used</t>
         </is>
@@ -29896,32 +29900,32 @@
       <c r="F56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>SalesCollection</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>SalesMeasureUnitCode</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>(presence signal, not mapped)</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>product.template</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>SalesCollection; presence sets sale_ok=True</t>
         </is>
@@ -29984,32 +29988,36 @@
       <c r="F59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>ProductCategoryCollection</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Electrical spares</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>product.template</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr"/>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>product.category</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>This is the CATEGORY's own description, mapped separately to product.category.name on sheet #58 - not the product's name</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -30149,26 +30157,22 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>ProductCategoryCollection</t>
-        </is>
-      </c>
+      <c r="F65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>MaterialValuationDataCollection</t>
+          <t>PlanningCollection</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>CompanyID</t>
+          <t>DemandManagementProcedureCode</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>ATOS_CPC</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -30186,17 +30190,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>MaterialValuationDataCollection</t>
+          <t>PlanningCollection</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>CompanyUUID</t>
+          <t>DemandManagementProcedureCodeText</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>00163E74-9C3D-1ED8-BA91-477F3C01BF74</t>
+          <t>All demand consumes current forecasts</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -30214,17 +30218,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>MaterialValuationDataCollection</t>
+          <t>PlanningCollection</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>CreationDateTime</t>
+          <t>GoodsReceiptProcessingDuration</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>/Date(1544501523438)/</t>
+          <t>PT0H0M0S</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -30242,17 +30246,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>MaterialValuationDataCollection</t>
+          <t>PlanningCollection</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>LastChangeDateTime</t>
+          <t>LifeCycleStatusCode</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>/Date(1599494200030)/</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -30268,51 +30272,47 @@
       <c r="F69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>MaterialValuationDataCollection</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>MaterialUUID</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>00163E74-9C6C-1ED8-BF9F-5D3D00C1D488</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>(join key)</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>PlanningCollection</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>LifeCycleStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>product.template</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>vmumaterialvaluationdata's MaterialValuationDataCollection</t>
-        </is>
-      </c>
+      <c r="F70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>MaterialValuationDataCollection</t>
+          <t>PlanningCollection</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>MateriallID</t>
+          <t>LotSizeRoundingQuantity</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.00000000000000</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -30328,79 +30328,75 @@
       <c r="F71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>MaterialValuationDataCollection</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>ObjectID</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>00163E749C6C1ED8BF9F5D3D00C69488</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>id (external ID key)</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>PlanningCollection</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>LotSizeRoundingQuantityUnitCode</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>product.template</t>
         </is>
       </c>
-      <c r="F72" s="4" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>ValuationPriceCollection</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>19.410000</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>standard_price</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>PlanningCollection</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>LotSizeRoundingQuantityUnitCodeText</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Each</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>product.template</t>
         </is>
       </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>ValuationPriceCollection, latest by StartDate</t>
-        </is>
-      </c>
+      <c r="F73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>ValuationPriceCollection</t>
+          <t>PlanningCollection</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>AmountCurrencyCode</t>
+          <t>LotSizingMethodCode</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -30418,17 +30414,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>ValuationPriceCollection</t>
+          <t>PlanningCollection</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>BaseQuantity</t>
+          <t>LotSizingMethodCodeText</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>1.00000000000000</t>
+          <t>Lot-for-Lot</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -30446,17 +30442,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>ValuationPriceCollection</t>
+          <t>PlanningCollection</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>BaseQuantityUnitCode</t>
+          <t>MaximumLotSizeQuantity</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>ZNO</t>
+          <t>0.00000000000000</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -30474,17 +30470,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>ValuationPriceCollection</t>
+          <t>PlanningCollection</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>CreationDateTime</t>
+          <t>MaximumLotSizeQuantityUnitCode</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>/Date(1551440731370)/</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -30502,17 +30498,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>ValuationPriceCollection</t>
+          <t>PlanningCollection</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>EndDate</t>
+          <t>MaximumLotSizeQuantityUnitCodeText</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>/Date(253402214400000)/</t>
+          <t>Each</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -30530,19 +30526,15 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>ValuationPriceCollection</t>
+          <t>PlanningCollection</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>InventoryPriceChangedIndicator</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>MinimumDaysOfSupplyDuration</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr"/>
       <c r="D79" s="2" t="inlineStr">
         <is>
           <t>(not mapped)</t>
@@ -30558,17 +30550,17 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>ValuationPriceCollection</t>
+          <t>PlanningCollection</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>LastChangeDateTime</t>
+          <t>MinimumLotSizeQuantity</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>/Date(1551440731370)/</t>
+          <t>0.00000000000000</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -30584,47 +30576,47 @@
       <c r="F80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>ValuationPriceCollection</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>ObjectID</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>00163E749C3D1ED98F82F07EEB240B62</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>id (external ID key)</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>PlanningCollection</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>MinimumLotSizeQuantityUnitCode</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>product.template</t>
         </is>
       </c>
-      <c r="F81" s="4" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>ValuationPriceCollection</t>
+          <t>PlanningCollection</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>ParentObjectID</t>
+          <t>MinimumLotSizeQuantityUnitCodeText</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>00163E749C6C1EE8BE88D0153EBCD218</t>
+          <t>Each</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -30642,19 +30634,15 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>ValuationPriceCollection</t>
+          <t>PlanningCollection</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>PriceTypeCode</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>MinimumReceiptDaysOfSupplyDuration</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr"/>
       <c r="D83" s="2" t="inlineStr">
         <is>
           <t>(not mapped)</t>
@@ -30670,19 +30658,15 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>ValuationPriceCollection</t>
+          <t>PlanningCollection</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>PriceTypeCodeText</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Inventory Cost</t>
-        </is>
-      </c>
+          <t>MinimumShelfLifeDuration</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr"/>
       <c r="D84" s="2" t="inlineStr">
         <is>
           <t>(not mapped)</t>
@@ -30696,88 +30680,2652 @@
       <c r="F84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>ValuationPriceCollection</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>SetOfBooksDescription</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>DEAL_Set of Books</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>PlanningCollection</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C6C1ED8BF9F5D3D00C29488</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>id (external ID key)</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
         <is>
           <t>product.template</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>PlanningCollection</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>ParentObjectID</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>00163E749C6C1ED8BF9F5D3D00C1F488</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>PlanningCollection</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>PlanningGroupDescription</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr"/>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>PlanningCollection</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>PlanningGroupID</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr"/>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>PlanningCollection</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>PlanningProcedureCode</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>PlanningCollection</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>PlanningProcedureCodeText</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Demand-Driven Planning</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>PlanningCollection</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>PlanningTimeFenceDuration</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr"/>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>PlanningCollection</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>ProcurementLeadDuration</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>P70D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>PlanningCollection</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>PlanningCollection</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>ProcurementTypeCode</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>route_ids/id</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>'2' External Procurement -&gt; purchase_stock.route_warehouse0_buy, '1' In-house Production -&gt; mrp.route_warehouse0_manufacture. ASSUMES purchase_stock/mrp modules installed in target Odoo</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>PlanningCollection</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>ProcurementTypeCodeText</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>In-house Production</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>PlanningCollection</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>SafetyLeadDuration</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>P60D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>PlanningCollection</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>SafetyStockQuantity</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>0.00000000000000</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>PlanningCollection - belongs to stock.warehouse.orderpoint in Odoo, a separate model/master this pipeline doesn't build</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>PlanningCollection</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>SafetyStockQuantityUnitCode</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>PlanningCollection</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>SafetyStockQuantityUnitCodeText</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Each</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>PlanningCollection</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>SupplyPlanningAreaDescription</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Danlaw Technologies lndia Limited</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>PlanningCollection/AvailabilityConfirmationCollection</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>PlanningCollection</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>SupplyPlanningAreaID</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>71000</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>PlanningCollection/AvailabilityConfirmationCollection - MRP config, not a product.template field</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>PlanningCollection</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>SupplyPlanningAreaUUID</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>00163E74-9C6C-1EE8-BDDF-0A9B177C317C</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>IdentificationCollection</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C6C1ED8BF9F5D3D00C1D488</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>id (external ID key)</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>IdentificationCollection</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>ParentObjectID</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>00163E749C6C1ED8BF9F5D3D00C1D488</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>IdentificationCollection</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>ProductID</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Alternate/internal ID, redundant with default_code (only 'Internal ID' type present on this tenant)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>IdentificationCollection</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>ProductIdentifierTypeCode</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>IdentificationCollection</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>ProductIdentifierTypeCodeText</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Internal ID</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>LogisticsCollection</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>CycleCountPlannedDuration</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr"/>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>LogisticsCollection</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>LifeCycleStatusCode</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>LogisticsCollection</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>LifeCycleStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>LogisticsCollection</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C6C1ED8BF9F5D3D00C25488</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>id (external ID key)</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>LogisticsCollection</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>ParentObjectID</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>00163E749C6C1ED8BF9F5D3D00C1F488</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>LogisticsCollection</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>SiteID</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>71000</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>LogisticsCollection - site-specific, not a product attribute</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>LogisticsCollection</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>SiteName</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Danlaw Technologies lndia Limited</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>LogisticsCollection</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>LogisticsCollection</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>SiteUUID</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>00163E74-9C6C-1EE8-BDDE-E94AEAA5D059</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>ValuationCollection</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>BusinessResidenceID</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>71000</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>ValuationCollection</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>ValuationCollection</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>CompanyID</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>ValuationCollection - which company valuates this material; would need multi-company setup to use</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>ValuationCollection</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>LifeCycleStatusCode</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>ValuationCollection</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>LifeCycleStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>ValuationCollection</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C6C1ED8BF9F5D3D00C49488</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>id (external ID key)</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>ValuationCollection</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>ParentObjectID</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>00163E749C6C1ED8BF9F5D3D00C1F488</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>AvailabilityConfirmationCollection</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>AvailabilityCheckScopeCode</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>AvailabilityConfirmationCollection</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>AvailabilityCheckScopeCodeText</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>AvailabilityConfirmationCollection</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>GoodsIssueProcessingDuration</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>PT0H0M0S</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>AvailabilityConfirmationCollection</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>LifeCycleStatusCode</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>AvailabilityConfirmationCollection</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>LifeCycleStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>AvailabilityConfirmationCollection</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>ManualSourcingRequiredIndicator</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr"/>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>AvailabilityConfirmationCollection</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C6C1ED8BF9F5D3D00C21488</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>id (external ID key)</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>AvailabilityConfirmationCollection</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>ParentObjectID</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>00163E749C6C1ED8BF9F5D3D00C1F488</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>AvailabilityConfirmationCollection</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>SupplyPlanningAreaDescription</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Danlaw Technologies lndia Limited</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>PlanningCollection/AvailabilityConfirmationCollection</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>AvailabilityConfirmationCollection</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>SupplyPlanningAreaID</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>71000</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>PlanningCollection/AvailabilityConfirmationCollection - MRP config, not a product.template field</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>PlanningForecastGroupCollection</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C6C1ED8BF9F5D3D00C3D488</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>id (external ID key)</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>PlanningForecastGroupCollection</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>ParentObjectID</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>00163E749C6C1ED8BF9F5D3D00C1F488</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>PlanningForecastGroupCollection</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>ProductCategoryDescription</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Electrical spares</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>PlanningForecastGroupCollection</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>ProductCategoryInternalID</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Z302</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Forecast grouping, not the real category - see ProductCategoryCollection instead</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>QuantityConversionCollection</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>BatchDependentIndicator</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr"/>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>QuantityConversionCollection</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>CorrespondingQuantity</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>1.00000000000000</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>QuantityConversionCollection - unit conversion factor, only 5 rows on this tenant</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>QuantityConversionCollection</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>CorrespondingQuantityUnitCode</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>QuantityConversionCollection</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>CorrespondingQuantityUnitCodeText</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Kilogram</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>QuantityConversionCollection</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>00163EA8F2A11EEC87B4567E58BBB516</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>id (external ID key)</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>QuantityConversionCollection</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>ParentObjectID</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>00163EA8F2A11EEC87B4567E58BA7516</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>QuantityConversionCollection</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>1.00000000000000</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>QuantityConversionCollection</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>QuantityUnitCode</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>QuantityConversionCollection</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>QuantityUnitCodeText</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Each</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>DeviantTaxClassificationCollection</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>CountryCode</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>DeviantTaxClassificationCollection - per-country tax override; needs Taxes master #2, still pending. Only 4 rows on this tenant</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>DeviantTaxClassificationCollection</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>CountryCodeText</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>DeviantTaxClassificationCollection</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C6C1EE98FE270137808BCB5</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>id (external ID key)</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>DeviantTaxClassificationCollection</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>ParentObjectID</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>00163E749C6C1EE98FE25EC7653EFC4C</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>DeviantTaxClassificationCollection</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>RegionCode</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>DeviantTaxClassificationCollection</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>RegionCodeText</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Ordino</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>DeviantTaxClassificationCollection</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>TaxExemptionReasonCode</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr"/>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>DeviantTaxClassificationCollection</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>TaxExemptionReasonCodeText</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr"/>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>DeviantTaxClassificationCollection</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>TaxRateTypeCode</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>DeviantTaxClassificationCollection</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>TaxRateTypeCodeText</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>DeviantTaxClassificationCollection</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>TaxTypeCode</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>DeviantTaxClassificationCollection</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>DeviantTaxClassificationCollection</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>TaxTypeCodeText</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>State GST</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>MaterialValuationDataCollection</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>CompanyID</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>ValuationCollection - which company valuates this material; would need multi-company setup to use</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>MaterialValuationDataCollection</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>CompanyUUID</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>00163E74-9C3D-1ED8-BA91-477F3C01BF74</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>MaterialValuationDataCollection</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>CreationDateTime</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>/Date(1544501523438)/</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>MaterialValuationDataCollection</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>LastChangeDateTime</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>/Date(1599494200030)/</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>MaterialValuationDataCollection</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>MaterialUUID</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>00163E74-9C6C-1ED8-BF9F-5D3D00C1D488</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>(join key)</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>vmumaterialvaluationdata's MaterialValuationDataCollection</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>MaterialValuationDataCollection</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>MateriallID</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>MaterialValuationDataCollection</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C6C1ED8BF9F5D3D00C69488</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="inlineStr">
+        <is>
+          <t>id (external ID key)</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F162" s="4" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
           <t>ValuationPriceCollection</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>19.410000</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>standard_price</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>ValuationPriceCollection, latest by StartDate</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>ValuationPriceCollection</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>AmountCurrencyCode</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>ValuationPriceCollection</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>BaseQuantity</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>1.00000000000000</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>ValuationPriceCollection</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>BaseQuantityUnitCode</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>ZNO</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>ValuationPriceCollection</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>CreationDateTime</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>/Date(1551440731370)/</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>ValuationPriceCollection</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>EndDate</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>/Date(253402214400000)/</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>ValuationPriceCollection</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>InventoryPriceChangedIndicator</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>ValuationPriceCollection</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>LastChangeDateTime</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>/Date(1551440731370)/</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>ValuationPriceCollection</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C3D1ED98F82F07EEB240B62</t>
+        </is>
+      </c>
+      <c r="D171" s="4" t="inlineStr">
+        <is>
+          <t>id (external ID key)</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F171" s="4" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>ValuationPriceCollection</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>ParentObjectID</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>00163E749C6C1EE8BE88D0153EBCD218</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>ValuationPriceCollection</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>PriceTypeCode</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>ValuationPriceCollection</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>PriceTypeCodeText</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Inventory Cost</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>ValuationPriceCollection</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>SetOfBooksDescription</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>DEAL_Set of Books</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>ValuationPriceCollection</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>SetOfBooksID</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
         <is>
           <t>DSOB</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>product.template</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>ValuationPriceCollection</t>
         </is>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>StartDate</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
         <is>
           <t>/Date(1551398400000)/</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>(used to pick latest price, not mapped)</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>product.template</t>
         </is>
       </c>
-      <c r="F87" s="4" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>ValuationPriceCollection</t>
         </is>

--- a/SAP_Field_Mapping.xlsx
+++ b/SAP_Field_Mapping.xlsx
@@ -11426,7 +11426,7 @@
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="59" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>From WorkplaceAddressCollection, joined by ParentObjectID</t>
+          <t>From WorkplaceAddressCollection. ParentObjectID there is a 64-char CONCATENATION of two ObjectIDs - joined on its first 32 chars (full-string join matched 0/7). Only 7 of 99 employees have a workplace address in SAP</t>
         </is>
       </c>
     </row>
@@ -12273,7 +12273,11 @@
           <t>res.users</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Available in WorkplaceAddressCollection; Odoo res.users has no mobile field (res.partner does)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -12359,7 +12363,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>From WorkplaceAddressCollection</t>
+          <t>From WorkplaceAddressCollection, same 32-char join</t>
         </is>
       </c>
     </row>
@@ -12915,7 +12919,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1/2=Open, 4/5=Won/Lost - used to split crm_lead_open.csv / crm_lead_closed.csv</t>
+          <t>1/2=Open, 4/5=Won/Lost - used to split crm_lead_open.csv / crm_lead_closed.csv. Odoo stage_id is NOT set: CRM stages are per-database config and ByDesign's sales-phase codes don't map onto them</t>
         </is>
       </c>
     </row>
@@ -13995,7 +13999,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1/2=Open, 4/5=Won/Lost - used to split crm_lead_open.csv / crm_lead_closed.csv</t>
+          <t>1/2=Open, 4/5=Won/Lost - used to split crm_lead_open.csv / crm_lead_closed.csv. Odoo stage_id is NOT set: CRM stages are per-database config and ByDesign's sales-phase codes don't map onto them</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15079,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1/2=Open, 4/5=Won/Lost - used to split crm_lead_open.csv / crm_lead_closed.csv</t>
+          <t>1/2=Open, 4/5=Won/Lost - used to split crm_lead_open.csv / crm_lead_closed.csv. Odoo stage_id is NOT set: CRM stages are per-database config and ByDesign's sales-phase codes don't map onto them</t>
         </is>
       </c>
     </row>
@@ -19008,12 +19012,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="53" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
@@ -19538,32 +19542,32 @@
       <c r="F22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>ProductionOrderCollection</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>ObjectID</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>00163E749C3D1ED98E9AB40870669113</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>id (external ID key)</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>MainProductOutput.ExpectedScrapPercent</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0.000000</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>mrp.production</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -19573,12 +19577,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>PriorityCode</t>
+          <t>MainProductOutput.FulfilledQuantity</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.00000000000000</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -19601,12 +19605,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>PriorityCodeText</t>
+          <t>MainProductOutput.FulfilledQuantityUnitCode</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>ZNO</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -19629,12 +19633,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ProductionModelExplosionDate</t>
+          <t>MainProductOutput.FulfilledQuantityUnitCodeText</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>/Date(1550793600000)/</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -19657,12 +19661,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>ProductionModelID</t>
+          <t>MainProductOutput.ObjectID</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>CS90861BOOO_1</t>
+          <t>00163E749C3D1ED98E9AB408706DD113</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -19685,12 +19689,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ProductionModelVersionID</t>
+          <t>MainProductOutput.OpenQuantity</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>100.00000000000000</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -19713,12 +19717,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>ReleaseDateTime</t>
+          <t>MainProductOutput.OpenQuantityUnitCode</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>/Date(1550747880000)/</t>
+          <t>ZNO</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -19734,32 +19738,32 @@
       <c r="F29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>ProductionOrderCollection</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>RequestedEndDateTime</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>/Date(1551076200000)/</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>date_planned_finished</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>MainProductOutput.OpenQuantityUnitCodeText</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>mrp.production</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -19769,17 +19773,17 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>RequestedStartDateTime</t>
+          <t>MainProductOutput.PlannedQuantity</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>/Date(1550834280000)/</t>
+          <t>100.00000000000000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>date_planned_start</t>
+          <t>product_qty</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -19787,7 +19791,11 @@
           <t>mrp.production</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Via $expand=MainProductOutput</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -19797,12 +19805,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SchedulingStatusCode</t>
+          <t>MainProductOutput.PlannedQuantityUnitCode</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>ZNO</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -19815,7 +19823,11 @@
           <t>mrp.production</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Via $expand; Odoo takes the qty in the product's own UoM</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -19825,12 +19837,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SchedulingStatusCodeText</t>
+          <t>MainProductOutput.PlannedQuantityUnitCodeText</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -19846,60 +19858,64 @@
       <c r="F33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>ProductionOrderCollection</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>SiteID</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>71000</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>MainProductOutput.ProductID</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>CS90861BOOO</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>product_id/id</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>mrp.production</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Pulled via $expand=MainProductOutput - MainProductOutputCollection's own endpoint has no ParentObjectID and its ObjectIDs don't match the order's, so $expand is the only reliable link</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>ProductionOrderCollection</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>SiteName</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Danlaw Technologies lndia Limited</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C3D1ED98E9AB40870669113</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>id (external ID key)</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>mrp.production</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -19909,12 +19925,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>UUID</t>
+          <t>PriorityCode</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>00163E74-9C3D-1ED9-8E9A-B40870669113</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -19932,17 +19948,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>MainProductOutputCollection</t>
+          <t>ProductionOrderCollection</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>ExpectedScrapPercent</t>
+          <t>PriorityCodeText</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0.000000</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -19960,17 +19976,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>MainProductOutputCollection</t>
+          <t>ProductionOrderCollection</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>FulfilledQuantity</t>
+          <t>ProductionModelExplosionDate</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0.00000000000000</t>
+          <t>/Date(1550793600000)/</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -19988,17 +20004,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>MainProductOutputCollection</t>
+          <t>ProductionOrderCollection</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>FulfilledQuantityUnitCode</t>
+          <t>ProductionModelID</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>ZNO</t>
+          <t>CS90861BOOO_1</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -20016,17 +20032,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>MainProductOutputCollection</t>
+          <t>ProductionOrderCollection</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>FulfilledQuantityUnitCodeText</t>
+          <t>ProductionModelVersionID</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -20042,103 +20058,103 @@
       <c r="F40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>MainProductOutputCollection</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>ObjectID</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>00163E749C3D1ED98E9AB408706DD113</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>id (external ID key)</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>ReleaseDateTime</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>/Date(1550747880000)/</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>mrp.production</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>MainProductOutputCollection</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>OpenQuantity</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>100.00000000000000</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>RequestedEndDateTime</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1551076200000)/</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>date_planned_finished</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>mrp.production</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>MainProductOutputCollection</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>OpenQuantityUnitCode</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>ZNO</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>RequestedStartDateTime</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1550834280000)/</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>date_planned_start</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>mrp.production</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>MainProductOutputCollection</t>
+          <t>ProductionOrderCollection</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>OpenQuantityUnitCodeText</t>
+          <t>SchedulingStatusCode</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -20156,17 +20172,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>MainProductOutputCollection</t>
+          <t>ProductionOrderCollection</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>PlannedQuantity</t>
+          <t>SchedulingStatusCodeText</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>100.00000000000000</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -20184,17 +20200,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>MainProductOutputCollection</t>
+          <t>ProductionOrderCollection</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>PlannedQuantityUnitCode</t>
+          <t>SiteID</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>ZNO</t>
+          <t>71000</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -20212,17 +20228,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>MainProductOutputCollection</t>
+          <t>ProductionOrderCollection</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>PlannedQuantityUnitCodeText</t>
+          <t>SiteName</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Danlaw Technologies lndia Limited</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -20240,17 +20256,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>MainProductOutputCollection</t>
+          <t>ProductionOrderCollection</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>ProductID</t>
+          <t>UUID</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>CS90861BOOO</t>
+          <t>00163E74-9C3D-1ED9-8E9A-B40870669113</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -20268,17 +20284,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>OperationCollection</t>
+          <t>ProductionOrderCollection</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>CategoryCode</t>
+          <t>__metadata.type</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>cust.ProductionOrder</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -20296,17 +20312,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>OperationCollection</t>
+          <t>ProductionOrderCollection</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>CategoryCodeText</t>
+          <t>__metadata.uri</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Supply</t>
+          <t>https://my345654.sapbydesign.com/sap/byd/odata/cust/v1/khpro...</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -20322,47 +20338,47 @@
       <c r="F50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>OperationCollection</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>SO-1</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>MainProductOutputCollection</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>ExpectedScrapPercent</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>0.000000</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>mrp.production</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>OperationCollection</t>
+          <t>MainProductOutputCollection</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>MainResourceCategoryCode</t>
+          <t>FulfilledQuantity</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.00000000000000</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -20380,17 +20396,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>OperationCollection</t>
+          <t>MainProductOutputCollection</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>MainResourceCategoryCodeText</t>
+          <t>FulfilledQuantityUnitCode</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Equipment Resource</t>
+          <t>ZNO</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -20406,75 +20422,75 @@
       <c r="F53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>OperationCollection</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>MainProductOutputCollection</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>FulfilledQuantityUnitCodeText</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>MainProductOutputCollection</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>ObjectID</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>00163E749C3D1ED98E9AB4087066F113</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C3D1ED98E9AB408706DD113</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>id (external ID key)</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>mrp.production</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>OperationCollection</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>ParentObjectID</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>00163E749C3D1ED98E9AB40870669113</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>mrp.production</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>OperationCollection</t>
+          <t>MainProductOutputCollection</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>ProcessingNetDuration</t>
+          <t>OpenQuantity</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>PT0S</t>
+          <t>100.00000000000000</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -20492,17 +20508,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>OperationCollection</t>
+          <t>MainProductOutputCollection</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>ResourceCategoryCode</t>
+          <t>OpenQuantityUnitCode</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ZNO</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -20520,17 +20536,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>OperationCollection</t>
+          <t>MainProductOutputCollection</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>ResourceCategoryCodeText</t>
+          <t>OpenQuantityUnitCodeText</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Equipment Resource</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -20548,17 +20564,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>OperationCollection</t>
+          <t>MainProductOutputCollection</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>ResourceDescription</t>
+          <t>PlannedQuantity</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>MANUAL INSERTION OF COMPONENTS</t>
+          <t>100.00000000000000</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -20576,17 +20592,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>OperationCollection</t>
+          <t>MainProductOutputCollection</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>ResourceID</t>
+          <t>PlannedQuantityUnitCode</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>10400</t>
+          <t>ZNO</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -20604,17 +20620,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>OperationCollection</t>
+          <t>MainProductOutputCollection</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>ResourceProductionSchedulingRelevanceIndicator</t>
+          <t>PlannedQuantityUnitCodeText</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -20632,17 +20648,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>OperationCollection</t>
+          <t>MainProductOutputCollection</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>TypeCode</t>
+          <t>ProductID</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>CS90861BOOO</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -20665,12 +20681,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>TypeCodeText</t>
+          <t>CategoryCode</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Supply</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -20693,25 +20709,417 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
+          <t>CategoryCodeText</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>SO-1</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>MainResourceCategoryCode</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>MainResourceCategoryCodeText</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Equipment Resource</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C3D1ED98E9AB4087066F113</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>id (external ID key)</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>ParentObjectID</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>00163E749C3D1ED98E9AB40870669113</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>ProcessingNetDuration</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>PT0S</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>ResourceCategoryCode</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>ResourceCategoryCodeText</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Equipment Resource</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>ResourceDescription</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>MANUAL INSERTION OF COMPONENTS</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>ResourceID</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>10400</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>ResourceProductionSchedulingRelevanceIndicator</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>TypeCode</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>TypeCodeText</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>00163E74-9C3D-1ED9-8E9A-B4087066F113</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>mrp.production</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23924,7 +24332,7 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="51" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26289,7 +26697,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>From SupplierCollection, joined by ParentObjectID</t>
+          <t>From SupplierCollection (3529 rows for 655 POs - bundles several party roles). Resolved type-aware: prefers a PartyID that is a known SUPPLIER in res_partner.csv. Measured 91% valid vs 67% when taking the first row</t>
         </is>
       </c>
     </row>

--- a/SAP_Field_Mapping.xlsx
+++ b/SAP_Field_Mapping.xlsx
@@ -848,9 +848,9 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>pending_mapping</t>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>built</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1848,9 +1848,9 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>pending_mapping</t>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>built</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1888,9 +1888,9 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>pending_mapping</t>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>built</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -12575,7 +12575,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr"/>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>BLOCKED BY AUTHORISATION, not by a missing service: khlead is imported and live, but every one of its 19 entity sets returns RBAM_ERROR (Not Authorized) for the SDK user. Granting that user the Leads work center makes it readable - an SAP role change, not another import.</t>
+        </is>
+      </c>
     </row>
     <row r="4"/>
     <row r="5">
@@ -18550,10 +18554,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18566,20 +18575,1497 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Module: Inventory  |  Category: Transaction  |  Mandatory: Optional  |  Odoo model: stock.picking  |  Status: PENDING_MAPPING</t>
+          <t>Module: Inventory  |  Category: Transaction  |  Mandatory: Optional  |  Odoo model: stock.picking  |  Status: BUILT</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr"/>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>REAL DATA: khinbounddelivery - 49 inbound deliveries with 119 items. This is the receipts side; outbound deliveries were already covered as #64. Quantities live in a separate ItemQuantityCollection keyed on the item's ObjectID, not on the item row itself. picking_type_id is written as Odoo's built-in stock.picking_type_in rather than an external ID of ours.</t>
+        </is>
+      </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>No SAP data extracted yet for this object - see the notes above and CLAUDE.md.</t>
-        </is>
-      </c>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Entity (raw source)</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Field Name</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Sample Value</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Mapped Odoo Field</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Target Odoo Model</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>InboundDeliveryCollection</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>CancellationStatusCode</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>InboundDeliveryCollection</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>CancellationStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Not Canceled</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>InboundDeliveryCollection</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>ConsistencyStatusCode</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>InboundDeliveryCollection</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>ConsistencyStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Consistent</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>InboundDeliveryCollection</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>CreationDateTime</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1546943768439)/</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>InboundDeliveryCollection</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>DeliveryNoteStatusCode</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>InboundDeliveryCollection</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>DeliveryNoteStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>InboundDeliveryCollection</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>DeliveryProcessingStatusCode</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>InboundDeliveryCollection</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>DeliveryProcessingStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>InboundDeliveryCollection</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>8012019</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>InboundDeliveryCollection</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>IncotermsClassificationCode</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>EXW</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>InboundDeliveryCollection</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>IncotermsClassificationCodeText</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Ex works</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>InboundDeliveryCollection</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>IncotermsTransferLocationName</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>InboundDeliveryCollection</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>LastChangeDateTime</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1546943768439)/</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>InboundDeliveryCollection</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C6C1ED984E61ABEBD9FF46D</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>InboundDeliveryCollection</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>ProcessingTypeCode</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>CRD</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>InboundDeliveryCollection</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>ProcessingTypeCodeText</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Customer Return</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>InboundDeliveryCollection</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>ReleaseStatusCode</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>InboundDeliveryCollection</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>ReleaseStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Not Released</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>InboundDeliveryCollection</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>00163E74-9C6C-1ED9-84E6-1ABEBD9FF46D</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>CancellationStatusCode</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>CancellationStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Not Canceled</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>ConsistencyStatusCode</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>ConsistencyStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Consistent</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>CustomerReturnReasonCode</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>CustomerReturnReasonCodeText</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>No reason</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>IdentifiedStockID</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C6C1ED984E61ABEBDA0146D</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>ParentObjectID</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C6C1ED984E61ABEBD9FF46D</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>ProductID</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>ReleaseStatusCode</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>ReleaseStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Not Released</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>ReturnFollowupActivityCode</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>ReturnFollowupActivityCodeText</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Post to Own Stock</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>TypeCode</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>TypeCodeText</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Delivery Return Item</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>00163E74-9C6C-1ED9-84E6-1ABEBDA0146D</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>ItemQuantityCollection</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C6C1ED984E61ABEBDA0546D</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>ItemQuantityCollection</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>ParentObjectID</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C6C1ED984E61ABEBDA0146D</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>ItemQuantityCollection</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>4.00000000000000</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>ItemQuantityCollection</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>QuantityOriginCode</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr"/>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>ItemQuantityCollection</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>QuantityOriginCodeText</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr"/>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>ItemQuantityCollection</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>QuantityRoleCode</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ItemQuantityCollection</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>QuantityRoleCodeText</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Delivery Quantity</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>ItemQuantityCollection</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>QuantityTypeCode</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>ItemQuantityCollection</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>QuantityTypeCodeText</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>ItemQuantityCollection</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>UnitCode</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>ItemQuantityCollection</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>UnitCodeText</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Each</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>SenderPartyCollection</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C6C1ED984E61ABEBDA2D46D</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>SenderPartyCollection</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>ParentObjectID</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C6C1ED984E61ABEBD9FF46D</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>SenderPartyCollection</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>PartyID</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>1120645</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>stock.picking</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18592,10 +20078,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18608,20 +20099,1845 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Module: Inventory  |  Category: Transaction  |  Mandatory: Optional  |  Odoo model: stock.move  |  Status: PENDING_MAPPING</t>
+          <t>Module: Inventory  |  Category: Transaction  |  Mandatory: Optional  |  Odoo model: stock.move  |  Status: BUILT</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr"/>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>REAL DATA: khgoodsandserviceacknowledgement - 137 goods/service receipts with 238 lines carrying the product, delivered quantity and posting date. NOT from khgoodsandactivityconfirmation, which would have been the more direct inventory-movement source: that service is imported and most of it works, but its InventoryChangeItemCollection and header both return HTTP 500 from SAP on any request, unchanged after a re-import - an SAP-side defect, not a query problem.</t>
+        </is>
+      </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>No SAP data extracted yet for this object - see the notes above and CLAUDE.md.</t>
-        </is>
-      </c>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Entity (raw source)</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Field Name</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Sample Value</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Mapped Odoo Field</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Target Odoo Model</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>ApprovalStatusCode</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>ApprovalStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Approval not Necessary</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>CancellationDocumentIndicator</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>CancellationStatusCode</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>CancellationStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Not Canceled</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>ConsistencyStatusCode</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>ConsistencyStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Consistent</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>CreationDateTime</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1551078371000)/</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>CurrencyCode</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>CurrencyCodeText</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Indian Rupee</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>DataOriginTypeCode</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>DataOriginTypeCodeText</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Manual data entry</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1551052800000)/</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>GoodsReturnStatusCode</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>GoodsReturnStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Not Returned</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>LastChangeDateTime</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1551078371000)/</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>LifeCycleStatusCode</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>LifeCycleStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C3D1ED98E9978713A49672E</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>PostingDate</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1551052800000)/</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>ProcessingTypeCode</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>CONF</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>ProcessingTypeCodeText</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Goods and Service Acknowledgement</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>ReleaseStatusCode</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>ReleaseStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>TypeCode</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>GoodsAndServiceAcknowledgementCollection</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>TypeCodeText</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Goods And Service Confirmation</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>AcceptanceStatusCode</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>AcceptanceStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>CancellationStatusCode</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>CancellationStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Not Canceled</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>DeliveredQuantity</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>10.00000000000000</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>DeliveredQuantityUnitCode</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>ZNO</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>DeliveredQuantityUnitCodeText</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>DeliveryEndDateTime</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1551099600000)/</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>DeliveryEndTimeZoneCode</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>DeliveryStartDateTime</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1551013200000)/</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>DeliveryStartTimeZoneCode</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Sugar and tea</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>GoodsReturnStatusCode</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>GoodsReturnStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Not Returned</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>ItemLifeCycleStatusCode</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>ItemLifeCycleStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>NetAmount</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>20000.000000</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>NetAmountCurrencyCode</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>NetAmountCurrencyCodeText</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Indian Rupee</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>NetUnitPriceAmount</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>2000.000000</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>NetUnitPriceAmountBaseQuantity</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>1.00000000000000</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>NetUnitPriceAmountBaseQuantityUnitCode</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>ZNO</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>NetUnitPriceAmountCurrencyCode</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C3D1ED98E9978713A4EE72E</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>OpenQuantityCancelledIndicator</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr"/>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>ParentObjectID</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C3D1ED98E9978713A49672E</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>ProductCategoryInternalID</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>OTH</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>ProductID</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>SIA9680013050</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>ProductSellerID</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr"/>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>TotalDeliveredQuantity</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>0.00000000000000</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>TotalDeliveredQuantityUnitCode</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr"/>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>TotalDeliveredQuantityUnitCodeText</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr"/>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>TypeCode</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>TypeCodeText</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>SellerPartyCollection</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C3D1ED98E9978713A49A72E</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>SellerPartyCollection</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>ParentObjectID</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C3D1ED98E9978713A49672E</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>SellerPartyCollection</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>PartyID</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>stock.move</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -45100,10 +48416,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -45116,20 +48437,273 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Module: Accounts  |  Category: Master  |  Mandatory: Optional  |  Odoo model: account.analytic.account  |  Status: PENDING_MAPPING</t>
+          <t>Module: Accounts  |  Category: Master  |  Mandatory: Optional  |  Odoo model: account.analytic.account  |  Status: BUILT</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr"/>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>REAL DATA: khprofitcentre - 19 profit centres, ByDesign's second analytic dimension alongside the cost centres already built as #6. They share the one synthetic analytic plan Odoo requires. The readable name comes from a date-versioned NameCollection, not from the profit centre record itself, which carries only ID/ObjectID/UUID. khproject would add project-based analytic accounts too, but it is authorisation-blocked (RBAM_ERROR) - see SAP_IMPORT_PLAN.md.</t>
+        </is>
+      </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>No SAP data extracted yet for this object - see the notes above and CLAUDE.md.</t>
-        </is>
-      </c>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Entity (raw source)</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Field Name</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Sample Value</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Mapped Odoo Field</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Target Odoo Model</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>ProfitCentreCollection</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>71000</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>account.analytic.account</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>ProfitCentreCollection</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C3D1ED8BA914D7C501AFFBE</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>account.analytic.account</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>ProfitCentreCollection</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>00163E74-9C3D-1ED8-BA91-4D7C501AFFBE</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>account.analytic.account</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>NameCollection</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>EndDate</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>/Date(253402214400000)/</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>account.analytic.account</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>NameCollection</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>EMS-Electronic Manufacturing Service</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>account.analytic.account</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>NameCollection</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C3D1ED8BA915458C7AF7FD4</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>account.analytic.account</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>NameCollection</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>ParentObjectID</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C3D1ED8BA9151B19316BFCA</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>account.analytic.account</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>NameCollection</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>StartDate</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>/Date(680918400000)/</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>account.analytic.account</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/SAP_Field_Mapping.xlsx
+++ b/SAP_Field_Mapping.xlsx
@@ -2368,9 +2368,9 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>pending_mapping</t>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>built</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2528,9 +2528,9 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>pending_mapping</t>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>built</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Transaction</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2968,9 +2968,9 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>pending_mapping</t>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>built</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -25034,10 +25034,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="49" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25050,20 +25055,1293 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Module: Manufacturing  |  Category: Transaction  |  Mandatory: Optional  |  Odoo model: mrp.production  |  Status: PENDING_MAPPING</t>
+          <t>Module: Manufacturing  |  Category: Transaction  |  Mandatory: Optional  |  Odoo model: mrp.production  |  Status: BUILT</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr"/>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>REAL DATA: the closed subset of the same khproductionorder source as #44. LifeCycleStatusCodeText is real and populated (Started 86, Released 41, Finished 17, In Preparation 7, Canceled 1); Finished and Canceled are the terminal states, giving 18 historical orders.</t>
+        </is>
+      </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>No SAP data extracted yet for this object - see the notes above and CLAUDE.md.</t>
-        </is>
-      </c>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Entity (raw source)</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Field Name</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Sample Value</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Mapped Odoo Field</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Target Odoo Model</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>BillOfMaterialID</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>CS90861BOOO</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>BillOfOperationsID</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>CS90861BOOO</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>CreationDateTime</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1551082578761)/</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>EarliestEndDateTime</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1551071400000)/</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>EarliestStartDateTime</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1550834280000)/</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>EarliestStartDateTimeChangedIndicator</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>LastChangeDateTime</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1551451991756)/</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>LatestEndDateTime</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1551076200000)/</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>LatestEndDateTimeChangedIndicator</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>LatestStartDateTime</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1550834280000)/</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>LifeCycleStatusCode</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>LifeCycleStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>LogisticsAutomaticOutputRuleCode</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>LogisticsAutomaticOutputRuleCodeText</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr"/>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>LogisticsTaskGenerationStrategyCode</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>LogisticsTaskGenerationStrategyCodeText</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Reporting Point including Operations and Activities</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>MainProductOutput.ExpectedScrapPercent</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>0.000000</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>MainProductOutput.FulfilledQuantity</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>0.00000000000000</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>MainProductOutput.FulfilledQuantityUnitCode</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>ZNO</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>MainProductOutput.FulfilledQuantityUnitCodeText</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>MainProductOutput.ObjectID</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C3D1ED98E9AB408706DD113</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>MainProductOutput.OpenQuantity</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>100.00000000000000</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>MainProductOutput.OpenQuantityUnitCode</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>ZNO</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>MainProductOutput.OpenQuantityUnitCodeText</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>MainProductOutput.PlannedQuantity</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>100.00000000000000</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>MainProductOutput.PlannedQuantityUnitCode</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>ZNO</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>MainProductOutput.PlannedQuantityUnitCodeText</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>MainProductOutput.ProductID</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>CS90861BOOO</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C3D1ED98E9AB40870669113</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>PriorityCode</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>PriorityCodeText</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>ProductionModelExplosionDate</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1550793600000)/</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>ProductionModelID</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>CS90861BOOO_1</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>ProductionModelVersionID</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>ReleaseDateTime</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1550747880000)/</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>RequestedEndDateTime</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1551076200000)/</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>RequestedStartDateTime</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1550834280000)/</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>SchedulingStatusCode</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>SchedulingStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>SiteID</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>71000</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>SiteName</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Danlaw Technologies lndia Limited</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>00163E74-9C3D-1ED9-8E9A-B40870669113</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>__metadata.type</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>cust.ProductionOrder</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ProductionOrderCollection</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>__metadata.uri</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>https://my345654.sapbydesign.com/sap/byd/odata/cust/v1/khpro...</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>mrp.production</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -28354,10 +29632,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28370,24 +29653,857 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Module: Purchase  |  Category: Transaction  |  Mandatory: Optional  |  Odoo model: purchase.order  |  Status: PENDING_MAPPING</t>
+          <t>Module: Purchase  |  Category: Transaction  |  Mandatory: Optional  |  Odoo model: purchase.order  |  Status: BUILT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Filter: purchase.order in draft/sent state</t>
+          <t>REAL DATA: ByDesign has no separate RFQ object - an RFQ is a purchase order not yet ordered. LifeCycleStatusCodeText splits the 655 orders cleanly: In Preparation 89 + In Approval 86 = 175 pre-order documents (this file), against Sent/Follow-Up/Finished which are live orders already covered by #50.</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>No SAP data extracted yet for this object - see the notes above and CLAUDE.md.</t>
-        </is>
-      </c>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Entity (raw source)</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Field Name</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Sample Value</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Mapped Odoo Field</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Target Odoo Model</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>AcknowledgmentStatusCode</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>AcknowledgmentStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>No Acknowledgment Expected</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>ConsistencyStatusCode</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>ConsistencyStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Consistent</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>CreationDateTime</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1551078080000)/</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>CurrencyCode</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>CurrencyCodeText</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Indian Rupee</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>DataOriginTypeCode</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>DataOriginTypeCodeText</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Manual data entry</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>DeliveryStatusCode</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>DeliveryStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>IncotermsCode</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>EXW</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>IncotermsCodeText</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Ex works</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>IncotermsLocationName</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>InvoicingStatusCode</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>InvoicingStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>LastChangeDateTime</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1551078371000)/</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>LifeCycleStatusCode</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>LifeCycleStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Follow-Up Document Created</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C3D1ED98E9959AD7A2325C3</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>PreventDocumentOutputIndicator</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>TotalGrossAmount</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>23600.000000</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>TotalNetAmount</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>20000.000000</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>TotalTaxAmount</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>3600.000000</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>PurchaseOrderCollection</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>00163E74-9C3D-1ED9-8E99-59AD7A2325C3</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>SupplierCollection</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C3D1ED98E9959AD7A2365C3</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>SupplierCollection</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>ParentObjectID</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C3D1ED98E9959AD7A2325C3</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SupplierCollection</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>PartyID</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -41280,10 +43396,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -41296,24 +43417,1685 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Module: Sales  |  Category: Master  |  Mandatory: Optional  |  Odoo model: product.pricelist.item  |  Status: PENDING_MAPPING</t>
+          <t>Module: Sales  |  Category: Transaction  |  Mandatory: Optional  |  Odoo model: product.pricelist.item  |  Status: BUILT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>khsalesarrangement (#59's source) is header-only - no discount-rule line items found in it; would need a different/deeper entity not yet investigated</t>
+          <t>THIS TENANT HAS NO DISCOUNT RULES - checked, not assumed: of the 94 price components SAP categorises as 'Discount', every non-zero one is a Rounding Difference, and Item Discounts / Header Discounts are 0.00 throughout. Nothing was invented to fill the gap. What the same price-component data does carry is real LIST PRICES (269 components typed 'List Price', 97 distinct values), and product.pricelist.item is Odoo's model for 'this product is priced at X' - so this file holds 41 price rules under a dedicated 'SAP List Prices' pricelist, kept separate from the sales arrangements written for #59. Where a product was quoted at several prices the most frequent wins; the full per-order history is in output_full_csv/.</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>No SAP data extracted yet for this object - see the notes above and CLAUDE.md.</t>
-        </is>
-      </c>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Entity (raw source)</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Field Name</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Sample Value</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Mapped Odoo Field</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Target Odoo Model</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>ItemPriceComponentCollection</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>BaseDecimalValue</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>1.00000000000000</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>ItemPriceComponentCollection</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>BaseMeasureUnitCode</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>ItemPriceComponentCollection</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>BaseMeasureUnitCodeText</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Each</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>ItemPriceComponentCollection</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>CalculatedAmount</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>5000.000000</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>ItemPriceComponentCollection</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>CalculatedAmountCurrencyCode</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>ItemPriceComponentCollection</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>CalculatedAmountCurrencyCodeText</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Indian Rupee</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>ItemPriceComponentCollection</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>CalculationBasisAmount</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>0.000000</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>ItemPriceComponentCollection</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>CalculationBasisAmountCurrencyCode</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>ItemPriceComponentCollection</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>CalculationBasisQuantity</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>5.00000000000000</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>ItemPriceComponentCollection</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>CalculationBasisQuantityUnitCode</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>ItemPriceComponentCollection</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>CurrencyCode</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>ItemPriceComponentCollection</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>CurrencyCodeText</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Indian Rupee</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>ItemPriceComponentCollection</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>DecimalValue</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>1000.00000000000000</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>ItemPriceComponentCollection</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Total Item Net Value</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>ItemPriceComponentCollection</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>ManuallyChangedIndicator</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>ItemPriceComponentCollection</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>MeasureUnitCode</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>ItemPriceComponentCollection</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>MeasureUnitCodeText</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ItemPriceComponentCollection</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C3D1ED98ECDA5071DB2457B00163E749C3D1ED98ECDA8600158...</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>ItemPriceComponentCollection</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>ParentObjectID</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C3D1ED98ECDA5071DB2457B</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ItemPriceComponentCollection</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>TypeCode</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>0TTE</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>ItemPriceComponentCollection</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>TypeCodeText</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>CancellationStatusCode</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>CancellationStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Not Canceled</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>PCBA YSD SBW ILLUMINATION  BOARD</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>ExecutionReleaseStatusCode</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>ExecutionReleaseStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>ExternalItemReference</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>FulfilmentPartyCategoryCode</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>FulfilmentPartyCategoryCodeText</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>FulfilmentProcessingStatusCode</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>FulfilmentProcessingStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>InvoiceProcessingStatusCode</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>InvoiceProcessingStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>NetAmount</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>5000.000000</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>NetAmountCurrencyCode</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>NetAmountCurrencyCodeText</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Indian Rupee</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C3D1ED98ECDA5071DB2457B</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>ParentObjectID</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C3D1ED98ECD9DB5D4ADA563</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>PartialDeliveryControlCode</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>PartialDeliveryControlCodeText</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Multiple Deliveries</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>ProcessingTypeCode</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>TAN</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>ProcessingTypeCodeText</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Product - delivery-based</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>ProductAvailabilityConfirmationStatusCode</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>ProductAvailabilityConfirmationStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Confirmed Sufficiently</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>ReleaseStatusCode</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>ReleaseStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>TaxAmount</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>900.000000</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>TaxAmountCurrencyCode</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>TaxAmountCurrencyCodeText</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Indian Rupee</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>ItemCollection</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>00163E74-9C3D-1ED9-8ECD-A5071DB2457B</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>ItemProductCollection</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>IdentifiedStockID</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr"/>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>ItemProductCollection</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C3D1ED98ECDA5071DB2457B</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>ItemProductCollection</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>ParentObjectID</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>00163E749C3D1ED98ECDA5071DB2457B</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>ItemProductCollection</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>ProductID</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>ItemProductCollection</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>ProductRequirementSpecificationID</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr"/>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>ItemProductCollection</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>ProductStandardID</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr"/>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>ItemProductCollection</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>ProductTypeCode</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>ItemProductCollection</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>ProductTypeCodeText</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist.item</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/SAP_Field_Mapping.xlsx
+++ b/SAP_Field_Mapping.xlsx
@@ -2168,9 +2168,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>pending_mapping</t>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>built</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -13032,7 +13032,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>REAL DATA: same khlocation source as #28, filtered on InventoryManagedLocationIndicator (ByDesign's own signal for 'this location tracks inventory') - 1/4 locations qualify</t>
+          <t>REAL DATA: same khlocation source as #28, filtered on InventoryManagedLocationIndicator (ByDesign's own signal for 'this location tracks inventory') - 1/1 locations qualify as of 2026-09-25 (tenant used to have 4 sites; confirmed live it now has only 1, 'Danlaw Technologies India Limited' - a tenant-side change, not a pipeline gap)</t>
         </is>
       </c>
     </row>
@@ -13924,7 +13924,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>REAL DATA: khlocation custom service, 4 locations</t>
+          <t>REAL DATA: khlocation custom service, 1 site as of 2026-09-25 (was 4; confirmed live - see #27 note) plus its storage areas</t>
         </is>
       </c>
     </row>
@@ -19312,10 +19312,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19328,24 +19333,1125 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Module: Manufacturing  |  Category: Master  |  Mandatory: Yes  |  Odoo model: mrp.bom  |  Status: PENDING_MAPPING</t>
+          <t>Module: Manufacturing  |  Category: Master  |  Mandatory: Yes  |  Odoo model: mrp.bom  |  Status: BUILT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>NOT OBTAINABLE OVER ODATA FROM THIS TENANT - the strongest negative result in the project, and the one mandatory object that genuinely cannot be closed from here. Searched for bom / 'bill of material' / 'production model' / recipe / component / routing / explosion across BOTH (a) all 1485 entity sets of all 48 services the tenant publishes to this user (schema_snapshots/service_catalog.json, SERVICE_CATALOG.csv) and (b) all 609 entity sets defined across all 47 custom service .xml files - zero matches in either. Importing more custom services cannot produce it: no BOM service definition exists in the sample set. The design-time catalog does list PBOM data sources (SCMPBOMU02 etc), but they are NOT published as OData on this tenant - that catalog tracks report definitions, not published services. khproductionorder REFERENCES a BOM via ProductionModelID/ProductionModelVersionID but never exposes its components. Options for the user: expose the PBOM data sources via Business Configuration &gt; Analytics, or extract BOMs by a non-OData route (UI export / file download) and hand over a CSV.</t>
+          <t>REAL DATA, closed 2026-09-25. Confirmed unobtainable via the tenant's 1485 built-in + 609 custom-.xml entity sets (an exhaustive negative result, still true of THAT set) - but the data itself was real, visible live in the ByDesign UI under Enterprise Search &gt; 'Bills of Material Variants'. Closed by building a brand new custom OData service (khbomvariant) directly via the OData Editor - self-service, no .xml import needed - exposing the underlying ProductionBillOfMaterial standard Business Object for the first time. 400 BOM headers, 448 variants (447 non-obsolete -&gt; mrp_bom.csv rows), 14,947 component lines -&gt; mrp_bom_line.csv. product_tmpl_id/id and each line's product_id/id resolve via the same MaterialUUID -&gt; InternalID lookup used for product_template.csv (1/447 boms and 0/14947 lines unresolved). Verified against the live UI screen for one real BOM (CS90861DOOO): all 5 components shown on screen matched exactly (products + quantities), plus 8 more from other item groups not visible in that screen's scroll position. Known limitation: components attach to the BOM header, not a specific variant, so the 48 headers with multiple variants get the same component list per variant - matches what the raw data actually supports. Full story + screenshots: sap_odata_editor_walkthrough/bom_service_setup/README.md.</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>No SAP data extracted yet for this object - see the notes above and CLAUDE.md.</t>
-        </is>
-      </c>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Entity (raw source)</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Field Name</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Sample Value</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Mapped Odoo Field</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Target Odoo Model</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialCollection</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>PCBA FOR GEAR MOTOR</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialCollection</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>BGMBETTCARD7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>mrp.bom</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialCollection</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>LogisticsPreparationFunctionalUnitID</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialCollection</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>LogisticsPreparationFunctionalUnitUUID</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialCollection</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F7A721ED9898C36894601C402</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>(join key)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Header - looked up by ProductionBillOfMaterialVariantCollection.ParentObjectID</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialCollection</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F-7A72-1ED9-898C-36894601C402</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialVariantCollection</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Variant's own ID; mrp_bom.csv's code uses the header's ID instead</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialVariantCollection</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>MaterialUUID</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>00163E5F-7A72-1ED9-88DC-8CE74D155AE0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>product_tmpl_id/id</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>mrp.bom</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Via the same MaterialUUID -&gt; InternalID lookup used for product_template.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialVariantCollection</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>00163E5F7A721ED9898C368946022402</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>id (external ID key)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>mrp.bom</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialVariantCollection</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>ObsoleteIndicator</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>(filter only, not mapped)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Obsolete variants (1/448) excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialVariantCollection</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>ParentObjectID</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F7A721ED9898C36894601C402</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>(join key)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>-&gt; ProductionBillOfMaterialCollection.ObjectID</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialVariantCollection</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1.00000000000000</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>product_qty</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>mrp.bom</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialVariantCollection</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>unitCode</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>ZNO</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialItemGroupCollection</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>BillOfMaterialID</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>BGMBETTCARD7</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>(not used, not mapped)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialItemGroupCollection</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>BillOfMaterialItemGroupID</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>(not used, not mapped)</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialItemGroupCollection</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>(not used, not mapped)</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialItemGroupCollection</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>ItemRequiredIndicator</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>(not used, not mapped)</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialItemGroupCollection</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>MultipleSelectionAllowedIndicator</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>(not used, not mapped)</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialItemGroupCollection</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F7A721ED9898C368946028402</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>(not used, not mapped)</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Raw-extracted but not used - this entity is a thin pointer node with no component data of its own and a broken $expand back to its parent on this tenant; see build_boms() docstring. Real component data comes from ItemGroupItemChangeStateCollection instead</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialItemGroupCollection</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>ParentObjectID</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F7A721ED9898C36894601C402</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>(not used, not mapped)</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialItemGroupCollection</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F-7A72-1ED9-898C-368946028402</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>(not used, not mapped)</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialItemGroupItemChangeStateCollection</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>DeletedIndicator</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>(filter only, not mapped)</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom.line</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Deleted component lines excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialItemGroupItemChangeStateCollection</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>EngineeringChangeOrderID</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>BGMBETTCARD7</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom.line</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialItemGroupItemChangeStateCollection</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>MaterialUUID</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>00163E5F-7A72-1ED9-88DC-8CE74D157AE0</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>product_id/id</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>mrp.bom.line</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Component product, via the same MaterialUUID -&gt; InternalID lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialItemGroupItemChangeStateCollection</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F7A721ED9898C368946036402</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>(part of id)</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom.line</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Combined with the variant's ObjectID to form mrp_bom_line.csv's external id</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialItemGroupItemChangeStateCollection</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterial.Description</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>PCBA FOR GEAR MOTOR</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom.line</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>$expand artifact</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialItemGroupItemChangeStateCollection</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterial.ID</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>BGMBETTCARD7</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom.line</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>$expand artifact</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialItemGroupItemChangeStateCollection</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterial.LogisticsPreparationFunctionalUnitID</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom.line</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>$expand artifact</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialItemGroupItemChangeStateCollection</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterial.LogisticsPreparationFunctionalUnitUUID</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom.line</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>$expand artifact</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialItemGroupItemChangeStateCollection</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterial.ObjectID</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F7A721ED9898C36894601C402</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>(join key)</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom.line</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Populated via $expand=ProductionBillOfMaterial - the real BOM header link (ItemGroupItemCollection's own nav property back to its parent is broken on this tenant, see build_boms() docstring)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialItemGroupItemChangeStateCollection</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterial.UUID</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F-7A72-1ED9-898C-36894601C402</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom.line</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>$expand artifact</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialItemGroupItemChangeStateCollection</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>1.00000000000000</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>product_qty</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>mrp.bom.line</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialItemGroupItemChangeStateCollection</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>QuantityFixedIndicator</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom.line</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialItemGroupItemChangeStateCollection</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F-7A72-1ED9-898C-368946036402</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom.line</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialItemGroupItemChangeStateCollection</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>__metadata.type</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>cust.ProductionBillOfMaterialItemGroupItemChangeState</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>(technical, not mapped)</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom.line</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialItemGroupItemChangeStateCollection</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>__metadata.uri</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>https://my346623.sapbydesign.com/sap/byd/odata/cust/v1/khbom...</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>(technical, not mapped)</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom.line</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>ProductionBillOfMaterialItemGroupItemChangeStateCollection</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>unitCode</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>ZNO</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>mrp.bom.line</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19432,7 +20538,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>REAL DATA: derived from khproductionorder's OperationCollection (ResourceID/ResourceDescription), deduplicated - no dedicated Work Center master service found, but this data was already on hand (used for #44) - 18 distinct work centers</t>
+          <t>REAL DATA: derived from khproductionorder's OperationCollection (ResourceID/ResourceDescription), deduplicated - no dedicated Work Center master service found, but this data was already on hand (used for #44) - 17 distinct work centers as of 2026-09-25 (was 18 earlier - minor drift in the source data, negligible)</t>
         </is>
       </c>
     </row>
@@ -37964,7 +39070,11 @@
           <t>BankGroupCode</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
           <t>(not mapped)</t>
@@ -37988,7 +39098,11 @@
           <t>BankGroupCodeText</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Corporation Bank</t>
+        </is>
+      </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
           <t>(not mapped)</t>
@@ -38068,7 +39182,11 @@
           <t>CommonBankStandardIDMainIndicator</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
           <t>(not mapped)</t>
@@ -38148,7 +39266,11 @@
           <t>DeletedIndicator</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
           <t>(not mapped)</t>
@@ -38284,7 +39406,11 @@
           <t>RegionCode</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr"/>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
           <t>(not mapped)</t>
@@ -38308,7 +39434,11 @@
           <t>RegionCodeText</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr"/>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Goa</t>
+        </is>
+      </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
           <t>(not mapped)</t>
@@ -38332,7 +39462,11 @@
           <t>StreetName</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr"/>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Collyer Quay Branch</t>
+        </is>
+      </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
           <t>(not mapped)</t>
@@ -39468,7 +40602,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>REAL DATA: khsalesarrangement custom service, 35 arrangements. partner_id/id NOT populated - CustomerUUID here is a hyphenated GUID that doesn't match res_partner's numeric-ID-based external IDs, and this tenant hasn't exposed a UUID-&gt;numeric-ID lookup</t>
+          <t>REAL DATA: 226 pricelists, one per real SAP Sales Arrangement resolved from khsalesorder via _resolve_order_to_arrangement() (Customer + SalesOrg + DistributionChannel business key) - not one synthetic catch-all. partner_id/id NOT populated - CustomerUUID here is a hyphenated GUID that doesn't match res_partner's numeric-ID-based external IDs, and this tenant hasn't exposed a UUID-&gt;numeric-ID lookup</t>
         </is>
       </c>
     </row>
@@ -40192,7 +41326,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>THIS TENANT HAS NO DISCOUNT RULES - checked, not assumed: of the 94 price components SAP categorises as 'Discount', every non-zero one is a Rounding Difference, and Item Discounts / Header Discounts are 0.00 throughout. Nothing was invented to fill the gap. What the same price-component data does carry is real LIST PRICES (269 components typed 'List Price', 97 distinct values), and product.pricelist.item is Odoo's model for 'this product is priced at X' - so this file holds 41 price rules under a dedicated 'SAP List Prices' pricelist, kept separate from the sales arrangements written for #59. Where a product was quoted at several prices the most frequent wins; the full per-order history is in output_full_csv/.</t>
+          <t>THIS TENANT HAS NO DISCOUNT RULES - checked, not assumed: of the 94 price components SAP categorises as 'Discount', every non-zero one is a Rounding Difference, and Item Discounts / Header Discounts are 0.00 throughout. Nothing was invented to fill the gap. What the same price-component data does carry is real LIST PRICES, and product.pricelist.item is Odoo's model for 'this product is priced at X' - so this file holds 1109 price lines attached to their real resolved #59 pricelists (61 of 226 carry lines); only the 8 orders whose Sales Arrangement couldn't be resolved fall into a small 'SAP List Prices - Unmatched Sales Arrangement' fallback pricelist. Where a product was quoted at several prices the most frequent wins; the full per-order history is in output_full_csv/.</t>
         </is>
       </c>
     </row>

--- a/SAP_Field_Mapping.xlsx
+++ b/SAP_Field_Mapping.xlsx
@@ -1928,9 +1928,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>not_in_bydesign</t>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>built</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -12628,7 +12628,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>REAL DATA: khopportunity custom service, 15 opportunities (all, unfiltered)</t>
+          <t>khopportunity custom service - transform code is real and correct, but confirmed live on 2026-09-26 (direct curl, $inlinecount=allpages) that OpportunityCollection currently has 0 rows on this tenant - down from the 15 this note previously described. Not a pipeline bug: crm_lead.csv/_open/_closed are correctly empty because the source data is currently empty. Re-check live if this matters before go-live; the code will pick up real rows automatically the moment the tenant has any.</t>
         </is>
       </c>
     </row>
@@ -12704,7 +12704,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>REAL DATA: same khopportunity source as #20, filtered on LifeCycleStatusCode (Open=1, In Process=2) - 8/15 open</t>
+          <t>Same khopportunity source and same currently-empty-tenant caveat as #20 (filter logic: LifeCycleStatusCode Open=1/In Process=2, confirmed correct in code, just has nothing to filter right now).</t>
         </is>
       </c>
     </row>
@@ -12780,7 +12780,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>REAL DATA: same khopportunity source as #20, filtered on LifeCycleStatusCode (Won=4, Lost=5) - 7/15 closed</t>
+          <t>Same khopportunity source and same currently-empty-tenant caveat as #20 (filter logic: LifeCycleStatusCode Won=4/Lost=5, confirmed correct in code, just has nothing to filter right now).</t>
         </is>
       </c>
     </row>
@@ -19010,10 +19010,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19026,22 +19031,387 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Module: Maintenance  |  Category: Master  |  Mandatory: Yes  |  Odoo model: maintenance.equipment  |  Status: NOT_IN_BYDESIGN</t>
+          <t>Module: Maintenance  |  Category: Master  |  Mandatory: Yes  |  Odoo model: maintenance.equipment  |  Status: BUILT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>MANDATORY - investigated twice. (1) Zero matches for 'equipment' across the tenant's 573-entry Design Data Sources catalog. (2) User imported+tested tmserviceorder/tmserviceconfirmation/tmservicerequest (Service Order/Confirmation/Request custom services) as a possible alternate path: their metadata confirms NO standalone Equipment entity exists in any of them - ReferenceObjectCollection only carries ProductID(+SerialID), i.e. ByDesign models 'equipment' as a serialized Product instance, not separate master data. tmserviceorder/tmservicerequest data access is additionally blocked by SAP authorization restrictions for the SDK user (metadata visible, data reads return RBAM_ERROR); tmserviceconfirmation is accessible but has 0 rows on this tenant. CONCLUSION: standard ByDesign has no Equipment master data object - if this data is needed, it must come from a different source system or be confirmed out of scope with Danlaw/the client.</t>
+          <t>MANDATORY - closed 2026-09-28. Earlier notes (kept for context) correctly found no standalone 'Equipment' master data object in any standard or custom service - ByDesign genuinely has no Preventive Maintenance module. What resolves the sheet requirement instead: the real ByDesign standard Business Object EquipmentResource ('Supply Chain Design Master Data' -&gt; 'Resources' in the live UI, the same discovery as khbomvariant) - 18 real records (SMT lines, wave soldering, final inspection, etc.), genuinely typed 'Equipment Resource' on this tenant. Never published as OData until built directly via the OData Editor (self-service, no .xml import): service khequipmentresource, Work Center View SCM_RESOURCES (found by searching the picker for 'Resources' - it only matches a Work Center View's own display name, not its technical ID or parent Work Center name, which is why 'Equipment'/'Design'/'Master Data' searches all returned zero results first). See build_equipment() in src/transform_odoo.py; raw_sources below.</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>No SAP data extracted yet for this object - see the notes above and CLAUDE.md.</t>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Entity (raw source)</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Field Name</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Sample Value</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Mapped Odoo Field</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Target Odoo Model</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>EquipmentResourceCollection</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>CategoryCode</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>maintenance.equipment</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>EquipmentResourceCollection</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>SMT LINES WITH PRINTER, SPI, PLACEMENT &amp;</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>maintenance.equipment</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>EquipmentResourceCollection</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>FinancialRelevanceIndicator</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>maintenance.equipment</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>EquipmentResourceCollection</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>10100</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>serial_no</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>maintenance.equipment</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>The resource's own business ID, e.g. "10100"</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>EquipmentResourceCollection</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>00163E5F7A721EE989AE67C5DD490CF0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>id (external ID key)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>maintenance.equipment</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>EquipmentResourceCollection</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>ProductionSchedulingRelevanceIndicator</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>maintenance.equipment</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>EquipmentResourceCollection</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>ResourceMultipleIndicator</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>maintenance.equipment</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>EquipmentResourceCollection</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>ResourceTimeZoneCode</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>maintenance.equipment</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>EquipmentResourceCollection</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>SupplyPlanningRelevanceIndicator</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>maintenance.equipment</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>EquipmentResourceCollection</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F-7A72-1EE9-89AE-67C5DD490CF0</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>maintenance.equipment</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>EquipmentResourceCollection</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>WorkingDayCalendarCode</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Z98Z</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>maintenance.equipment</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>EquipmentResourceCollection</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>languageCode</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>(filter only)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>maintenance.equipment</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Always EN on this tenant</t>
         </is>
       </c>
     </row>
@@ -43083,7 +43453,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>khcustomerquote custom service is imported and live (metadata confirmed, CustomerQuoteCollection has real fields) but data reads are blocked by SAP authorization restrictions for the SDK user (RBAM_ERROR) - needs broader permissions granted on this tenant before it can be extracted</t>
+          <t>UPDATED 2026-09-26: the authorization block described here is resolved - live curl now returns HTTP 200 with $inlinecount __count=0 (not RBAM_ERROR). khcustomerquote is imported, live, and authorized; the tenant genuinely just has zero customer quotes right now. Still pending_mapping because there's no data to confirm a transform against, not because of access - re-check if the tenant gets real quote data later.</t>
         </is>
       </c>
     </row>

--- a/SAP_Field_Mapping.xlsx
+++ b/SAP_Field_Mapping.xlsx
@@ -1088,9 +1088,9 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>pending_mapping</t>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>built</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1128,9 +1128,9 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>pending_mapping</t>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>built</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1168,9 +1168,9 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>pending_mapping</t>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>built</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1768,9 +1768,9 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>pending_mapping</t>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>built</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2288,9 +2288,9 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>pending_mapping</t>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>built</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3008,9 +3008,9 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>pending_mapping</t>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>built</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8166,10 +8166,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8182,24 +8187,313 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Module: Accounts  |  Category: Transaction  |  Mandatory: Optional  |  Odoo model: account.move  |  Status: PENDING_MAPPING</t>
+          <t>Module: Accounts  |  Category: Transaction  |  Mandatory: Optional  |  Odoo model: account.move  |  Status: BUILT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Data source confirmed: 'Journal Entry Item' (FINACCDIB), 'Journal Entry Voucher' (FINACCENB)</t>
+          <t>REAL DATA, closed 2026-09-28: fin_generalledger_analytics.svc/RPFINGLAU03_Q0001QueryResults ('Journal Entries'). Was 'data source confirmed' but never actually pulled - the report 400'd on every request because of a real bug in get_entity_set_all_fields() (BYD_P_* parameter fields, e.g. BYD_P_TARCUR, weren't being excluded from bulk $select the way P_*/PARA_* fields already were - see src/sap_client.py). 157 real G/L line items, genuinely balanced (net debit-credit ~0 across the whole file, confirmed). KCBALANCE_CURRCOMP is signed (positive=debit, negative=credit), so line_ids/debit and line_ids/credit are derived directly from its sign, not guessed.</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>No SAP data extracted yet for this object - see the notes above and CLAUDE.md.</t>
-        </is>
-      </c>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Entity (raw source)</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Field Name</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Sample Value</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Mapped Odoo Field</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Target Odoo Model</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>RPFINGLAU03_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>CACC_DOC_UUID</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>110000000649</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>id (external ID key) / ref</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>account.move</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>RPFINGLAU03_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>CCOMPANY_UUID</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>account.move</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>RPFINGLAU03_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>CDEBITCREDIT</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>(sign only, not mapped)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>account.move</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Used to decide whether KCBALANCE_CURRCOMP becomes a debit or a credit line</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>RPFINGLAU03_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>CDOC_DATE</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>/Date(1784160000000)/</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>account.move</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>RPFINGLAU03_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>CFISCYEAR</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>account.move</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>RPFINGLAU03_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>CGLACCT</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>151000</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>line_ids/account_id/id</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>account.move</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>RPFINGLAU03_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>KCBALANCE_CURRCOMP</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>5672328</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>line_ids/debit or line_ids/credit</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>account.move</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Signed - positive splits to debit, negative (as abs) to credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>RPFINGLAU03_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>RCBALANCE_CURRCOMP</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>account.move</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Always INR on this tenant</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>RPFINGLAU03_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>TGLACCT</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Accounts Payable-International</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field - also used to widen #1 Chart of Accounts)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>account.move</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8212,10 +8506,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8228,22 +8527,219 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Module: Accounts  |  Category: Transaction  |  Mandatory: Optional  |  Odoo model: account.asset  |  Status: PENDING_MAPPING</t>
+          <t>Module: Accounts  |  Category: Transaction  |  Mandatory: Optional  |  Odoo model: account.asset  |  Status: BUILT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Data source confirmed: 'Fixed Asset' (FINFXASSB), 'Fixed Assets Master Data' (FINFXAU04)</t>
+          <t>REAL DATA, closed 2026-09-28: fin_fixedassets_analytics.svc/RPFINFXAU04_Q0001QueryResults ('Fixed Assets - Master Data'), same BYD_P_* bug fix as #13. 3,279 real fixed assets (FACTORY LAND, LAPTOP, FEEDER F1-12, etc.).</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>No SAP data extracted yet for this object - see the notes above and CLAUDE.md.</t>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Entity (raw source)</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Field Name</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Sample Value</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Mapped Odoo Field</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Target Odoo Model</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>RPFINFXAU04_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>CASSETCLASS</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Z210</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>account.asset</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>RPFINFXAU04_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>CFXA_UUID</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>id (external ID key)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>account.asset</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>RPFINFXAU04_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>CLC_STAT</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>account.asset</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>RPFINFXAU04_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>TASSETCLASS</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Land - Leasehold</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>account.asset</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>RPFINFXAU04_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>TFXA_UUID</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>FACTORY LAND - L15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>account.asset</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>RPFINFXAU04_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>TLC_STAT</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Capitalized</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>(no core Odoo field)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>account.asset</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>e.g. "Capitalized"</t>
         </is>
       </c>
     </row>
@@ -8258,10 +8754,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8274,22 +8775,195 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Module: Accounts  |  Category: Transaction  |  Mandatory: Optional  |  Odoo model: account.asset.depreciation.line  |  Status: PENDING_MAPPING</t>
+          <t>Module: Accounts  |  Category: Transaction  |  Mandatory: Optional  |  Odoo model: account.asset.depreciation.line  |  Status: BUILT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Data source confirmed: 'Fixed Assets Values' (FINFXAU01)</t>
+          <t>REAL DATA, closed 2026-09-28: fin_fixedassets_analytics.svc/RPFINFXAU01_Q0001QueryResults ('Fixed Assets Values'), same fix as #13/#14. 1,565 rows - each asset's CURRENT accumulated depreciation position (KCPOSTED_DEPR), not a history of individual depreciation postings - no period dimension was selected, so this is one row per asset, not per-period. Called out explicitly rather than implying more granularity than the source actually gives.</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>No SAP data extracted yet for this object - see the notes above and CLAUDE.md.</t>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Entity (raw source)</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Field Name</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Sample Value</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Mapped Odoo Field</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Target Odoo Model</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>RPFINFXAU01_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>CFXA_UUID</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>id (external ID key) / asset_id/id</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>account.asset.depreciation.line</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>RPFINFXAU01_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>KCACCUMULATED_DEPR</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>-1535820.000000</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>(not used, not mapped)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>account.asset.depreciation.line</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>RPFINFXAU01_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>KCACQUISITION_COSTS</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>0.000000</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>(not used, not mapped)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>account.asset.depreciation.line</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Extracted but this object only writes the current depreciation position, not the full value history</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>RPFINFXAU01_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>KCNETBOOKVALUE_END_OF</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>0.000000</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>(not used, not mapped)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>account.asset.depreciation.line</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>RPFINFXAU01_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>KCPOSTED_DEPR</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0.000000</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>account.asset.depreciation.line</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Current accumulated depreciation position, not a per-period posting - see build_fixed_assets() docstring</t>
         </is>
       </c>
     </row>
@@ -12158,11 +12832,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -12186,7 +12860,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>REAL DATA: the G/L Account Master report (FINGLAU17) is live but declares a mandatory Chart of Accounts variable with no default and no readable value list, so it returns 0 rows. Built instead by unioning the six analytics reports that expose CGLACCT/TGLACCT without a blocking variable - see src/probe_gl_accounts.py, which tested all 60 candidate reports. Covers every G/L account carrying postings; an account configured in ByDesign but never posted to would not appear. account_type is derived from the account number band, each band confirmed against the real account names (see ACCOUNT_TYPE_BANDS in src/transform_odoo.py).</t>
+          <t>REAL DATA: the G/L Account Master report (FINGLAU17) is live but declares a mandatory Chart of Accounts variable with no default and no readable value list, so it returns 0 rows. Built instead by unioning the six analytics reports that expose CGLACCT/TGLACCT without a blocking variable - see src/probe_gl_accounts.py, which tested all 60 candidate reports. Covers every G/L account carrying postings; an account configured in ByDesign but never posted to would not appear. account_type is derived from the account number band, each band confirmed against the real account names (see ACCOUNT_TYPE_BANDS in src/transform_odoo.py). Added 2026-09-28: a 7th source, RPFINGLAU03_Q0001QueryResults (Journal Entries, #13's source) - 6 real accounts used in journal postings weren't covered by the original six reports; adding this source closed the gap, confirmed zero orphaned account references from #13 afterward. 219 accounts total.</t>
         </is>
       </c>
     </row>
@@ -12538,6 +13212,266 @@
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Falls back to CGLACCT itself when blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>RPFINGLAU03_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>CACC_DOC_UUID</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>110000000649</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>account.account</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>RPFINGLAU03_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>CCOMPANY_UUID</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>account.account</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>RPFINGLAU03_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>CDEBITCREDIT</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>account.account</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>RPFINGLAU03_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>CDOC_DATE</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1784160000000)/</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>account.account</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>RPFINGLAU03_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>CFISCYEAR</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>account.account</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>RPFINGLAU03_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>CGLACCT</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>151000</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>code / id (external ID key)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>account.account</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Same field name/meaning across all 6 source reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>RPFINGLAU03_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>KCBALANCE_CURRCOMP</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>5672328</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>account.account</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>RPFINGLAU03_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>RCBALANCE_CURRCOMP</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>account.account</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>RPFINGLAU03_Q0001QueryResults</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>TGLACCT</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Accounts Payable-International</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>account.account</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Falls back to CGLACCT itself when blank</t>
         </is>
@@ -15192,10 +16126,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15208,24 +16147,801 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Module: Inventory  |  Category: Master  |  Mandatory: Optional  |  Odoo model: stock.lot  |  Status: PENDING_MAPPING</t>
+          <t>Module: Inventory  |  Category: Master  |  Mandatory: Optional  |  Odoo model: stock.lot  |  Status: BUILT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>BLOCKED, deliberately not written: khproductionorder/ProductionLotCollection has 145 rows but exposes only ObjectID and ID - no ParentObjectID and no product reference of any kind - so lots cannot be attached to a product, and Odoo's stock.lot requires product_id. A file built from this would be 100% unimportable. Fix is an import, not code: khgoodsandactivityconfirmation.xml carries SerialNumber and IdentifiedStock with their material links (SAP_IMPORT_PLAN.md, priority 1).</t>
+          <t>REAL DATA, closed 2026-09-28: khproductionorder/ProductionLotCollection (the originally investigated source) really is a dead end - ObjectID + ID only, no product reference. Built instead from khgoodsandactivityconfirmation/IdentifiedStockCollection (51,980 real batch records), joined to a product via InventoryChangeItemCollection, which links every IdentifiedStockUUID to a MaterialUUID - confirmed clean, every one of the 185,158 linked movement rows maps to exactly one material. 51,077 lots written, all with a resolved product_id.</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>No SAP data extracted yet for this object - see the notes above and CLAUDE.md.</t>
-        </is>
-      </c>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Entity (raw source)</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Field Name</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Sample Value</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Mapped Odoo Field</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Target Odoo Model</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>IdentifiedStockCollection</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>IdentifiedStockCollection</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>IdentifiedStockTypeCode</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>IdentifiedStockCollection</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>IdentifiedStockTypeCodeText</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Optional Specified Stock</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>IdentifiedStockCollection</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F7A721ED98AF12BEFCA469FBF</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>CustodianPartyUUID</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>IdentifiedStockUUID</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F-7A72-1EE9-8AF1-E0657D480331</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeReasonCode</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeReasonCodeText</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Initial Balance Setting</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>InventoryMovementDirectionCode</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>InventoryMovementDirectionCodeText</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Inventory receipt</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>InventoryRelevanceIndicator</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>InventoryRestrictedUseIndicator</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>LocationUUID</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F-7A72-1EE9-87A8-E185FB7F8E14</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>LogisticsAreaUUID</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F-7A72-1EE9-87DA-1D1BAF9560EF</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>MaterialUUID</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F-7A72-1ED9-88F7-44A0C3077B05</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F7A721ED98ADFC81C81E6455F</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>OwnerPartyUUID</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F-7A72-1EE9-87A8-1D692B73CA0C</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>ParentObjectID</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F7A721ED98ADFC81C81E6255F</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>PermanentEstablishmentUUID</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F-7A72-1EE9-87A8-35E9FA7EEA67</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>StockTypeCode</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>StockTypeCodeText</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Logistics Area</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>SupplyPlanningAreaUUID</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F-7A72-1EE9-87D9-FB8C3A1BE00F</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>TransferGroupID</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>TypeCode</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>TypeCodeText</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Material Inventory Change Item</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F-7A72-1ED9-8ADF-C81C81E6455F</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>stock.lot</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17102,15 +18818,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="58" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17130,7 +18846,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>REAL DATA: khgoodsandserviceacknowledgement - 137 goods/service receipts with 238 lines carrying the product, delivered quantity and posting date. NOT from khgoodsandactivityconfirmation, which would have been the more direct inventory-movement source: that service is imported and most of it works, but its InventoryChangeItemCollection and header both return HTTP 500 from SAP on any request, unchanged after a re-import - an SAP-side defect, not a query problem.</t>
+          <t>REAL DATA, rebuilt 2026-09-28 from a much larger source after team feedback flagged the previous version as incomplete. Was: khgoodsandserviceacknowledgement, 137 receipts / 238 lines. Now: khgoodsandactivityconfirmation's real inventory-movement ledger - 147,979 confirmations, 366,585 movement lines - already fully extracted in output_raw/ but never wired into a transform (the earlier note that its InventoryChangeItemCollection 500'd was true once but no longer is - re-confirmed extracting cleanly at full volume). Issue/receipt leg pairs on the same confirmation+material (105,903 of them, zero quantity mismatches) are merged into single two-sided stock.move rows with real source/destination logistics areas; every other row keeps its one known real location and uses Odoo's own built-in Suppliers/Customers/Inventory-adjustment virtual location for the side SAP genuinely didn't attach a second area to. 260,682 rows, 0 missing product_id, 0 missing quantity.</t>
         </is>
       </c>
     </row>
@@ -17170,17 +18886,17 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
+          <t>GoodsAndActivityConfirmationCollection</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>ApprovalStatusCode</t>
+          <t>BusinessTransactionDateTime</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>/Date(1548916200000)/</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -17198,19 +18914,15 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
+          <t>GoodsAndActivityConfirmationCollection</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ApprovalStatusCodeText</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Approval not Necessary</t>
-        </is>
-      </c>
+          <t>CancellationDocumentIndicator</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
           <t>(not mapped)</t>
@@ -17226,17 +18938,17 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
+          <t>GoodsAndActivityConfirmationCollection</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CancellationDocumentIndicator</t>
+          <t>CancellationStatusCode</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -17254,17 +18966,17 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
+          <t>GoodsAndActivityConfirmationCollection</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CancellationStatusCode</t>
+          <t>CancellationStatusCodeText</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Not Canceled</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -17282,17 +18994,17 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
+          <t>GoodsAndActivityConfirmationCollection</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CancellationStatusCodeText</t>
+          <t>CreationDateTime</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Canceled</t>
+          <t>/Date(1549560742093)/</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -17310,17 +19022,17 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
+          <t>GoodsAndActivityConfirmationCollection</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ConsistencyStatusCode</t>
+          <t>DocumentReferenceID</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8-1</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -17338,17 +19050,17 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
+          <t>GoodsAndActivityConfirmationCollection</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>ConsistencyStatusCodeText</t>
+          <t>DocumentReferenceTypeCode</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Consistent</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -17366,17 +19078,17 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
+          <t>GoodsAndActivityConfirmationCollection</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>CreationDateTime</t>
+          <t>DocumentReferenceTypeCodeText</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>/Date(1549698815000)/</t>
+          <t>Outbound Delivery</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -17394,17 +19106,17 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
+          <t>GoodsAndActivityConfirmationCollection</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CurrencyCode</t>
+          <t>DocumentReferenceUUID</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>00163E5F-7A72-1ED9-8B84-90AF427507AE</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -17422,17 +19134,17 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
+          <t>GoodsAndActivityConfirmationCollection</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CurrencyCodeText</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Indian Rupee</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -17450,17 +19162,17 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
+          <t>GoodsAndActivityConfirmationCollection</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>DataOriginTypeCode</t>
+          <t>InventoryStockMovementStatusCode</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -17478,17 +19190,17 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
+          <t>GoodsAndActivityConfirmationCollection</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>DataOriginTypeCodeText</t>
+          <t>InventoryStockMovementStatusCodeText</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Manual data entry</t>
+          <t>Adhoc Change</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -17504,47 +19216,51 @@
       <c r="F17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>/Date(1549670400000)/</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>GoodsAndActivityConfirmationCollection</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>00163E5F7A721ED98ADFC81C81E6255F</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>id (external ID key)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>stock.move</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>ItemCollection side</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
+          <t>GoodsAndActivityConfirmationCollection</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>GoodsReturnStatusCode</t>
+          <t>ReversalConfirmationID</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>335</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -17562,17 +19278,17 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
+          <t>GoodsAndActivityConfirmationCollection</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>GoodsReturnStatusCodeText</t>
+          <t>TransactionDateTime</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Not Returned</t>
+          <t>/Date(1548916200000)/</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -17590,17 +19306,17 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
+          <t>GoodsAndActivityConfirmationCollection</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>UUID</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>00163E5F-7A72-1ED9-8ADF-C81C81E6255F</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -17618,19 +19334,15 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
+          <t>InventoryChangeItemCollection</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>LastChangeDateTime</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>/Date(1551416578000)/</t>
-        </is>
-      </c>
+          <t>CustodianPartyUUID</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr"/>
       <c r="D22" s="4" t="inlineStr">
         <is>
           <t>(not mapped)</t>
@@ -17646,17 +19358,17 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
+          <t>InventoryChangeItemCollection</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>LifeCycleStatusCode</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -17674,17 +19386,17 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
+          <t>InventoryChangeItemCollection</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>LifeCycleStatusCodeText</t>
+          <t>IdentifiedStockUUID</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Canceled</t>
+          <t>00163E5F-7A72-1EE9-8AF1-E0657D480331</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -17700,83 +19412,75 @@
       <c r="F24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>ObjectID</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>00163E5F7A721ED98B87CCDE4EC31707</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>id (external ID key)</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeReasonCode</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>stock.move</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>ItemCollection side</t>
-        </is>
-      </c>
+      <c r="F25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>PostingDate</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>/Date(1549670400000)/</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeReasonCodeText</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Initial Balance Setting</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>stock.move</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>From the GoodsAndServiceAcknowledgementCollection header</t>
-        </is>
-      </c>
+      <c r="F26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
+          <t>InventoryChangeItemCollection</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>ProcessingTypeCode</t>
+          <t>InventoryMovementDirectionCode</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -17794,17 +19498,17 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
+          <t>InventoryChangeItemCollection</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>ProcessingTypeCodeText</t>
+          <t>InventoryMovementDirectionCodeText</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Goods and Service Acknowledgement</t>
+          <t>Inventory receipt</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -17822,17 +19526,17 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
+          <t>InventoryChangeItemCollection</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>ReleaseStatusCode</t>
+          <t>InventoryRelevanceIndicator</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>True</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -17848,51 +19552,47 @@
       <c r="F29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>ReleaseStatusCodeText</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>InventoryRestrictedUseIndicator</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>stock.move</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>"Released" -&gt; done, else draft</t>
-        </is>
-      </c>
+      <c r="F30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
+          <t>InventoryChangeItemCollection</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>TypeCode</t>
+          <t>LocationUUID</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>00163E5F-7A72-1EE9-87A8-E185FB7F8E14</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -17910,17 +19610,17 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>GoodsAndServiceAcknowledgementCollection</t>
+          <t>InventoryChangeItemCollection</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>TypeCodeText</t>
+          <t>LogisticsAreaUUID</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Goods And Service Confirmation</t>
+          <t>00163E5F-7A72-1EE9-87DA-1D1BAF9560EF</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -17938,15 +19638,19 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>ItemCollection</t>
+          <t>InventoryChangeItemCollection</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>AcceptanceStatusCode</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr"/>
+          <t>MaterialUUID</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F-7A72-1ED9-88F7-44A0C3077B05</t>
+        </is>
+      </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
           <t>(not mapped)</t>
@@ -17960,43 +19664,51 @@
       <c r="F33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>ItemCollection</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>AcceptanceStatusCodeText</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr"/>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>00163E5F7A721ED98ADFC81C81E6455F</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>id (external ID key)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>stock.move</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>ItemCollection side</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>ItemCollection</t>
+          <t>InventoryChangeItemCollection</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>CancellationStatusCode</t>
+          <t>OwnerPartyUUID</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>00163E5F-7A72-1EE9-87A8-1D692B73CA0C</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -18014,17 +19726,17 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>ItemCollection</t>
+          <t>InventoryChangeItemCollection</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>CancellationStatusCodeText</t>
+          <t>ParentObjectID</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Canceled</t>
+          <t>00163E5F7A721ED98ADFC81C81E6255F</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -18040,75 +19752,75 @@
       <c r="F36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>ItemCollection</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>DeliveredQuantity</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>150.00000000000000</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>product_uom_qty</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>PermanentEstablishmentUUID</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F-7A72-1EE9-87A8-35E9FA7EEA67</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>stock.move</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>ItemCollection</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>DeliveredQuantityUnitCode</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>ZNO</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>product_uom/id</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>StockTypeCode</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>stock.move</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>ItemCollection</t>
+          <t>InventoryChangeItemCollection</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>DeliveredQuantityUnitCodeText</t>
+          <t>StockTypeCodeText</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Logistics Area</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -18126,17 +19838,17 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>ItemCollection</t>
+          <t>InventoryChangeItemCollection</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>DeliveryEndDateTime</t>
+          <t>SupplyPlanningAreaUUID</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>/Date(1549717200000)/</t>
+          <t>00163E5F-7A72-1EE9-87D9-FB8C3A1BE00F</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -18154,17 +19866,17 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>ItemCollection</t>
+          <t>InventoryChangeItemCollection</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>DeliveryEndTimeZoneCode</t>
+          <t>TransferGroupID</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -18182,17 +19894,17 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>ItemCollection</t>
+          <t>InventoryChangeItemCollection</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>DeliveryStartDateTime</t>
+          <t>TypeCode</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>/Date(1549630800000)/</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -18210,17 +19922,17 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>ItemCollection</t>
+          <t>InventoryChangeItemCollection</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>DeliveryStartTimeZoneCode</t>
+          <t>TypeCodeText</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>Material Inventory Change Item</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -18236,79 +19948,79 @@
       <c r="F43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>ItemCollection</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>TPKG -0031 corrugated boxes</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>InventoryChangeItemCollection</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F-7A72-1ED9-8ADF-C81C81E6455F</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>stock.move</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Falls back to ID when blank</t>
-        </is>
-      </c>
+      <c r="F44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>ItemCollection</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>GoodsReturnStatusCode</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>ItemChangeQuantityCollection</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>00163E5F7A721ED98ADFC81C81E6655F</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>id (external ID key)</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>stock.move</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>ItemCollection side</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>ItemCollection</t>
+          <t>ItemChangeQuantityCollection</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>GoodsReturnStatusCodeText</t>
+          <t>ParentObjectID</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Not Returned</t>
+          <t>00163E5F7A721ED98ADFC81C81E6455F</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -18326,17 +20038,17 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>ItemCollection</t>
+          <t>ItemChangeQuantityCollection</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>31.00000000000000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -18354,17 +20066,17 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>ItemCollection</t>
+          <t>ItemChangeQuantityCollection</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>ItemLifeCycleStatusCode</t>
+          <t>QuantityUnitCode</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>ZNO</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -18382,17 +20094,17 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>ItemCollection</t>
+          <t>ItemChangeQuantityCollection</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>ItemLifeCycleStatusCodeText</t>
+          <t>QuantityUnitCodeText</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Canceled</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -18406,598 +20118,6 @@
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>ItemCollection</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>NetAmount</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>25500.000000</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>stock.move</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>ItemCollection</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>NetAmountCurrencyCode</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>stock.move</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>ItemCollection</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>NetAmountCurrencyCodeText</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>Indian Rupee</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>stock.move</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>ItemCollection</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>NetUnitPriceAmount</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>170.000000</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>stock.move</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>ItemCollection</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>NetUnitPriceAmountBaseQuantity</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>1.00000000000000</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>stock.move</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>ItemCollection</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>NetUnitPriceAmountBaseQuantityUnitCode</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>ZNO</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>stock.move</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>ItemCollection</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>NetUnitPriceAmountCurrencyCode</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>stock.move</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>ItemCollection</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>ObjectID</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>00163E5F7A721ED98B87CCF57F05B707</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>id (external ID key)</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>stock.move</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>ItemCollection side</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>ItemCollection</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>OpenQuantityCancelledIndicator</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr"/>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>stock.move</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>ItemCollection</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>ParentObjectID</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>00163E5F7A721ED98B87CCDE4EC31707</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>stock.move</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>ItemCollection</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>ProductCategoryInternalID</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>OTH</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>stock.move</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>ItemCollection</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>ProductID</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>MCPM01ORNGMSMN</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>product_id/id</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>stock.move</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>ItemCollection</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>ProductSellerID</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr"/>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>stock.move</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>ItemCollection</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>TotalDeliveredQuantity</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>0.00000000000000</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>stock.move</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>ItemCollection</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>TotalDeliveredQuantityUnitCode</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>ZFT</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>stock.move</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>ItemCollection</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>TotalDeliveredQuantityUnitCodeText</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>Square Feet</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>stock.move</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>ItemCollection</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>TypeCode</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>stock.move</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>ItemCollection</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>TypeCodeText</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>stock.move</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>SellerPartyCollection</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>ObjectID</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>00163E5F7A721ED98B87CCDE4EC35707</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>id (external ID key)</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>stock.move</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>ItemCollection side</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>SellerPartyCollection</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>ParentObjectID</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>00163E5F7A721ED98B87CCDE4EC31707</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>stock.move</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>SellerPartyCollection</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>PartyID</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>70000</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>partner_id/id</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>stock.move</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>From SellerPartyCollection</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21408,10 +22528,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21424,20 +22549,513 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Module: Manufacturing  |  Category: Master  |  Mandatory: Optional  |  Odoo model: mrp.routing.workcenter  |  Status: PENDING_MAPPING</t>
+          <t>Module: Manufacturing  |  Category: Master  |  Mandatory: Optional  |  Odoo model: mrp.routing.workcenter  |  Status: BUILT</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr"/>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>REAL DATA, closed 2026-09-28: khproductionorder/OperationCollection was already raw-extracted (82,859 rows, one per operation per production order) but never transformed - #44's own docstring flagged this. Deduplicated by (operation ID, resource) among 'Make' rows to the real distinct operation types actually run on each work center - 22 combinations (SMT on 10100, AOI on 10200, wave soldering on 10500, etc.). Cycle time deliberately not included - ProcessingNetDuration is an observed per-order duration, not a standard planned time, so there is no single correct value without fabricating one.</t>
+        </is>
+      </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>No SAP data extracted yet for this object - see the notes above and CLAUDE.md.</t>
-        </is>
-      </c>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Entity (raw source)</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Field Name</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Sample Value</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Mapped Odoo Field</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Target Odoo Model</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>CategoryCode</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>(filter only)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>mrp.routing.workcenter</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>CategoryCodeText</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>mrp.routing.workcenter</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>SO-1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>name / (part of id)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>mrp.routing.workcenter</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Deduplicated with ResourceID to the 22 distinct real operation types - see build_routing_operations() docstring</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>MainResourceCategoryCode</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>mrp.routing.workcenter</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>MainResourceCategoryCodeText</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Equipment Resource</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>mrp.routing.workcenter</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F7A721ED98AF06F5041695BE0</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>mrp.routing.workcenter</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>ParentObjectID</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F7A721ED98AF06F504168FBE0</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>mrp.routing.workcenter</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>ProcessingNetDuration</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>PT0S</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>(not used, not mapped)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>mrp.routing.workcenter</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Per-order observed duration, not a standard planned time - deliberately not used as a template cycle time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>ResourceCategoryCode</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>mrp.routing.workcenter</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>ResourceCategoryCodeText</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Equipment Resource</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>mrp.routing.workcenter</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>ResourceDescription</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>SMT LINES WITH PRINTER, SPI, PLACEMENT &amp;</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>(not used, not mapped)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>mrp.routing.workcenter</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Same text as maintenance_equipment.csv's own name field</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>ResourceID</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>10100</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>workcenter_id/id / (part of id)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>mrp.routing.workcenter</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>ResourceProductionSchedulingRelevanceIndicator</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>mrp.routing.workcenter</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>TypeCode</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>mrp.routing.workcenter</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>TypeCodeText</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>(filter only)</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>mrp.routing.workcenter</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Only "Make" rows kept</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>OperationCollection</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F-7A72-1ED9-8AF0-6F5041695BE0</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>mrp.routing.workcenter</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -40944,11 +42562,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -40972,7 +42590,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>REAL DATA: 226 pricelists, one per real SAP Sales Arrangement resolved from khsalesorder via _resolve_order_to_arrangement() (Customer + SalesOrg + DistributionChannel business key) - not one synthetic catch-all. partner_id/id NOT populated - CustomerUUID here is a hyphenated GUID that doesn't match res_partner's numeric-ID-based external IDs, and this tenant hasn't exposed a UUID-&gt;numeric-ID lookup</t>
+          <t>REAL DATA: 226 pricelists, one per real SAP Sales Arrangement resolved from khsalesorder via _resolve_order_to_arrangement() (Customer + SalesOrg + DistributionChannel business key) - not one synthetic catch-all. partner_id/id populated as of 2026-09-28 via khcustomer/CustomerCollection's UUID-&gt;InternalID lookup (same pattern as vmumaterial for products) - 225/225 real sales arrangements resolved (the 226th row is the synthetic unmatched-orders fallback, which has no single customer by definition).</t>
         </is>
       </c>
     </row>
@@ -41178,34 +42796,34 @@
       <c r="F11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>SalesArrangementCollection</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>CustomerUUID</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>00163E5F-7A72-1ED9-888B-762B0CCF52EA</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>(not mapped)</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>partner_id/id</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>product.pricelist</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Hyphenated GUID doesn't match res_partner's numeric-ID external IDs - known limitation, see CLAUDE.md</t>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Resolved via khcustomer/CustomerCollection's UUID-&gt;InternalID lookup, closed 2026-09-28 - also closes #61</t>
         </is>
       </c>
     </row>
@@ -41656,6 +43274,1190 @@
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>ABCClassificationCode</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>ABCClassificationCodeText</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>A-Account</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>BusinessPartnerFormattedName</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>TE CONNECTIVITY INDIA PVT LTD (EOU</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>CategoryCode</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>CategoryCodeText</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Organization</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>CompanyLegalFormCode</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>CompanyLegalFormCodeText</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>ContactAllowedCode</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>ContactAllowedCodeText</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Allowed</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>CreationDateTime</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1548392338608)/</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>FulfilmentBlockingReasonCode</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>FulfilmentBlockingReasonCodeText</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>IndustrialSectorCode</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>IndustrialSectorCodeText</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>InternalID</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>1113761</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>InvoicingBlockingReasonCode</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr"/>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>InvoicingBlockingReasonCodeText</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr"/>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>LastChangeDateTime</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1693046060008)/</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>LegalCompetenceIndicator</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>LifeCycleStatusCode</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>LifeCycleStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>NielsenID</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr"/>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>NielsenIDText</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr"/>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>00163E5F7A721ED9888B75CEA3DFD2EA</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>id (external ID key)</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>OrderBlockingReasonCode</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr"/>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>OrderBlockingReasonCodeText</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr"/>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>OrganisationFirstLineName</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>TE CONNECTIVITY INDIA PVT LTD (EOU</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>OrganisationSecondLineName</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>TITAN COMPANY LTD</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>PersonAcademicTitleCode</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr"/>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>PersonAcademicTitleCodeText</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr"/>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>PersonBirthDate</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr"/>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>PersonBirthName</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr"/>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>PersonCommunicationLanguageCode</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr"/>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>PersonCommunicationLanguageCodeText</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr"/>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>PersonFamilyName</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr"/>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>PersonFormOfAddressCode</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr"/>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>PersonFormOfAddressCodeText</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr"/>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>PersonGenderCode</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr"/>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>PersonGenderCodeText</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr"/>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>PersonGivenName</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr"/>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>PersonMiddleName</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr"/>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>PersonNickName</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr"/>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>PersonProfessionCode</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr"/>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>PersonProfessionCodeText</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr"/>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>SortingFormattedName</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>TE CONNECTIVITY INDIA PVT LTD (EOU</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F-7A72-1ED9-888B-75CEA3DFD2EA</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -43384,10 +46186,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -43400,24 +46207,1881 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Module: Sales  |  Category: Master  |  Mandatory: Optional  |  Odoo model: product.pricelist  |  Status: PENDING_MAPPING</t>
+          <t>Module: Sales  |  Category: Master  |  Mandatory: Optional  |  Odoo model: product.pricelist  |  Status: BUILT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Same source as #59 but without a working partner link (see #59's note), so this isn't meaningfully 'by customer' yet - left pending until the UUID-&gt;partner mapping is solved</t>
+          <t>CLOSED 2026-09-28: same underlying file as #59 (product_pricelist.csv) - the UUID-&gt;partner mapping that blocked this is now solved (see #59's note), so every real pricelist genuinely carries its customer's partner_id/id and no separate file is needed to make this 'by customer'.</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>No SAP data extracted yet for this object - see the notes above and CLAUDE.md.</t>
-        </is>
-      </c>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Entity (raw source)</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>SAP Field Name</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Sample Value</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Mapped Odoo Field</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Target Odoo Model</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SalesArrangementCollection</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>CompleteDeliveryRequestedIndicator</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SalesArrangementCollection</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>CreationDateTime</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1548392338608)/</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SalesArrangementCollection</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>CurrencyCode</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SalesArrangementCollection</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>CurrencyCodeText</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Indian Rupee</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SalesArrangementCollection</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>CustomerGroupCode</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SalesArrangementCollection</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>CustomerGroupCodeText</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Private customer</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SalesArrangementCollection</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>CustomerUUID</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>00163E5F-7A72-1ED9-888B-762B0CCF52EA</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>partner_id/id</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Resolved via khcustomer/CustomerCollection's UUID-&gt;InternalID lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SalesArrangementCollection</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>DeliveryPriorityCode</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SalesArrangementCollection</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>DeliveryPriorityCodeText</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Urgent</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SalesArrangementCollection</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>DistributionChannelCode</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SalesArrangementCollection</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>DistributionChannelCodeText</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Direct sales</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SalesArrangementCollection</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>IncotermsCode</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>EXW</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SalesArrangementCollection</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>IncotermsCodeText</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Ex works</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SalesArrangementCollection</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>IncotermsLocationName</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>TIRUVELLORE</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>SalesArrangementCollection</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>LastChangeDateTime</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1548392338608)/</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>SalesArrangementCollection</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>LifeCycleStatusCode</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>SalesArrangementCollection</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>LifeCycleStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>SalesArrangementCollection</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F7A721ED9888BBD7687F2F460</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>SalesArrangementCollection</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>PaymentTermsCode</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>SalesArrangementCollection</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>PaymentTermsCodeText</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>30 days net</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>SalesArrangementCollection</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>SalesOrganisationID</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>71000</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>SalesArrangementCollection</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>SalesOrganisationUUID</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F-7A72-1EE9-87A8-35E9FA7EEA67</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>SalesArrangementCollection</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F-7A72-1ED9-888B-BD7687F2F460</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>ABCClassificationCode</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>ABCClassificationCodeText</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>A-Account</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>BusinessPartnerFormattedName</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>TE CONNECTIVITY INDIA PVT LTD (EOU</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>CategoryCode</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>CategoryCodeText</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Organization</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>CompanyLegalFormCode</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>CompanyLegalFormCodeText</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>ContactAllowedCode</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>ContactAllowedCodeText</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Allowed</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>CreationDateTime</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1548392338608)/</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>FulfilmentBlockingReasonCode</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>FulfilmentBlockingReasonCodeText</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>IndustrialSectorCode</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>IndustrialSectorCodeText</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>InternalID</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>1113761</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>InvoicingBlockingReasonCode</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr"/>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>InvoicingBlockingReasonCodeText</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr"/>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>LastChangeDateTime</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>/Date(1693046060008)/</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>LegalCompetenceIndicator</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>LifeCycleStatusCode</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>LifeCycleStatusCodeText</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>NielsenID</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr"/>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>NielsenIDText</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr"/>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F7A721ED9888B75CEA3DFD2EA</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>OrderBlockingReasonCode</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr"/>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>OrderBlockingReasonCodeText</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr"/>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>OrganisationFirstLineName</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>TE CONNECTIVITY INDIA PVT LTD (EOU</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>OrganisationSecondLineName</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>TITAN COMPANY LTD</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>PersonAcademicTitleCode</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr"/>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>PersonAcademicTitleCodeText</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr"/>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>PersonBirthDate</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr"/>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>PersonBirthName</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr"/>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>PersonCommunicationLanguageCode</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr"/>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>PersonCommunicationLanguageCodeText</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr"/>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>PersonFamilyName</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr"/>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>PersonFormOfAddressCode</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr"/>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>PersonFormOfAddressCodeText</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr"/>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>PersonGenderCode</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr"/>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>PersonGenderCodeText</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr"/>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>PersonGivenName</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr"/>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>PersonMiddleName</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr"/>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>PersonNickName</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr"/>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>PersonProfessionCode</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr"/>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>PersonProfessionCodeText</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr"/>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>SortingFormattedName</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>TE CONNECTIVITY INDIA PVT LTD (EOU</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>CustomerCollection</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>00163E5F-7A72-1ED9-888B-75CEA3DFD2EA</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>product.pricelist</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
